--- a/s-s-event-bogor/sessions/day-2/clinic/services/services_exercise.xlsx
+++ b/s-s-event-bogor/sessions/day-2/clinic/services/services_exercise.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,17 +57,11 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
       <color rgb="00006100"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -78,18 +72,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
         <bgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="003B9C7B"/>
-        <bgColor rgb="003B9C7B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="000A5455"/>
-        <bgColor rgb="000A5455"/>
       </patternFill>
     </fill>
     <fill>
@@ -125,27 +107,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -514,12 +486,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -532,7 +503,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Part A: Physical quantification | Part B: Monetary valuation</t>
+          <t>4 services: fish provisioning, carbon, recreation, coastal protection</t>
         </is>
       </c>
     </row>
@@ -579,391 +550,253 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Reef fish catch</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>180,000 kg/yr</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Reef fish catch</t>
+          <t>Average fish price</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>180,000 kg/yr</t>
+          <t>USD 3.50/kg</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Average fish price</t>
+          <t>Total fishing costs</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>USD 3.50/kg</t>
+          <t>USD 420,000/yr</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Total fishing costs</t>
+          <t>Mangrove NCP rate</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>USD 420,000/yr</t>
+          <t>3.7 Mg CO2/ha/yr</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Seagrass NCP rate</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>1.3 Mg CO2/ha/yr</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Mangrove NCP rate</t>
+          <t>Social cost of carbon</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>3.7 Mg CO2/ha/yr</t>
+          <t>USD 51/Mg CO2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Seagrass NCP rate</t>
+          <t>Reef visitors</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>1.3 Mg CO2/ha/yr</t>
+          <t>15,000/yr</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Social cost of carbon</t>
+          <t>Reef spending per visitor</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>USD 51/Mg CO2</t>
+          <t>USD 85</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Protected coastline</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>12,000 m</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Reef visitors</t>
+          <t>Seawall replacement cost</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>15,000/yr</t>
+          <t>USD 5,000/m</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Reef spending per visitor</t>
+          <t>Seawall lifespan</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>USD 85</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Protected coastline</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>12,000 m</t>
+          <t>50 years</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Seawall cost</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>USD 5,000/m</t>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Part 1: Fish Provisioning</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>Seawall lifespan</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>50 years</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>PART A: Physical Quantification</t>
-        </is>
-      </c>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Gross revenue</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Total costs</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Resource rent</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>A1: Carbon (Mg CO2/yr)</t>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Part 2: Carbon Sequestration</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>Mangrove: 350 x 3.7 =</t>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Mangrove physical (Mg CO2/yr)</t>
         </is>
       </c>
       <c r="B27" s="6" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Seagrass: 800 x 1.3 =</t>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Mangrove value (USD/yr)</t>
         </is>
       </c>
       <c r="B28" s="6" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Total carbon:</t>
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Seagrass physical (Mg CO2/yr)</t>
         </is>
       </c>
       <c r="B29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Seagrass value (USD/yr)</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Physical Supply Table (Part A)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
+          <t>Total carbon value (USD/yr)</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>Carbon sequestration</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>Mg CO2/yr</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="n"/>
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Part 3: Recreation</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>Fish provisioning</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>kg/yr</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>Coastal protection</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="n"/>
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Recreation value (USD/yr)</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>visitors/yr</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>PART B: Monetary Valuation</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>B1: Fish revenue (180,000 x 3.50) =</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>B1: Resource rent (revenue - 420,000) =</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>B2: Carbon value (total Mg CO2 x 51) =</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>B3: Recreation (15,000 x 85) =</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>B4: Coastal total (12,000 x 5,000) =</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>B4: Annualized (total / 50) =</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>Monetary Supply Table (Part B)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>Method</t>
-        </is>
-      </c>
-      <c r="C51" s="7" t="inlineStr">
-        <is>
-          <t>USD/yr</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="8" t="inlineStr">
-        <is>
-          <t>Fish provisioning</t>
-        </is>
-      </c>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>Resource rent</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="8" t="inlineStr">
-        <is>
-          <t>Carbon sequestration</t>
-        </is>
-      </c>
-      <c r="B53" s="9" t="inlineStr">
-        <is>
-          <t>SCC</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="8" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
-      <c r="B54" s="9" t="inlineStr">
-        <is>
-          <t>Direct expenditure</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="8" t="inlineStr">
-        <is>
-          <t>Coastal protection</t>
-        </is>
-      </c>
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t>Replacement cost</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="8" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B56" s="9" t="inlineStr"/>
-      <c r="C56" s="6" t="n"/>
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Part 4: Coastal Protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Total replacement cost (USD)</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Annualized value (USD/yr)</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -977,11 +810,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -992,197 +825,117 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Part A: Physical Supply</t>
-        </is>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Fish: Gross revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>630000</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>Carbon (mangrove)</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>1,295 Mg CO2/yr</t>
-        </is>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Fish: Resource rent</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>210000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>Carbon (seagrass)</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>1,040 Mg CO2/yr</t>
-        </is>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Mangrove carbon (Mg CO2/yr)</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>1295</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>Carbon total</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>2,335 Mg CO2/yr</t>
-        </is>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Mangrove carbon value (USD/yr)</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>66045</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Fish provisioning</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>180,000 kg/yr</t>
-        </is>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Seagrass carbon (Mg CO2/yr)</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>1040</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>Coastal protection</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>12,000 m</t>
-        </is>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Seagrass carbon value (USD/yr)</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>53040</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>15,000 visitors/yr</t>
-        </is>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Total carbon value (USD/yr)</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>119085</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Recreation value (USD/yr)</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>1275000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Coastal protection total (USD)</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>60000000</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Part B: Monetary Valuation</t>
-        </is>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Coastal protection annualized (USD/yr)</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>1200000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>Fish: gross revenue</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>USD 630,000</t>
-        </is>
-      </c>
+      <c r="A13" s="5" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>Fish: resource rent</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>USD 210,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>Carbon: mangrove</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>USD 66,045</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>Carbon: seagrass</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>USD 53,040</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>Carbon: total</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>USD 119,085</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>USD 1,275,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>Coastal: total replacement</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>USD 60,000,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>Coastal: annualized</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>USD 1,200,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>TOTAL (all services)</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>USD 2,804,085</t>
-        </is>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL ecosystem services (USD/yr)</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>2804085</v>
       </c>
     </row>
   </sheetData>

--- a/s-s-event-bogor/sessions/day-2/clinic/services/services_exercise.xlsx
+++ b/s-s-event-bogor/sessions/day-2/clinic/services/services_exercise.xlsx
@@ -7,8 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answers" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercise" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answers" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Glossary" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,8 +62,14 @@
       <color rgb="00006100"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -78,6 +86,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
         <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003B9C7B"/>
+        <bgColor rgb="003B9C7B"/>
       </patternFill>
     </fill>
   </fills>
@@ -107,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -119,6 +133,13 @@
     </xf>
     <xf numFmtId="3" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -482,6 +503,138 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="000A5455"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Ocean Accounting Clinic: Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Exercise Workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>How to use this file</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>This exercise helps you practice calculating ecosystem service values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>The exercise is split into two parts:</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Part A (Physical Quantification): calculate how much service the ecosystem provides</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Part B (Monetary Valuation): assign economic values to physical quantities</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Part A is a complete account on its own. Part B builds on Part A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Yellow cells: fill these in with your calculations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>The Answers sheet shows the correct values in green cells.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>What you are calculating:</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Physical supply: quantities in natural units (kilograms, tonnes CO2, metres, visitors)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Monetary value: economic values in USD per year</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Resource rent: revenue minus all costs (labour, fuel, gear, capital)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - SCC value: physical carbon sequestration multiplied by the Social Cost of Carbon price</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="003B9C7B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -507,6 +660,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -594,7 +748,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>3.7 Mg CO2/ha/yr</t>
+          <t>3.7 tonnes CO2/ha/yr</t>
         </is>
       </c>
     </row>
@@ -606,7 +760,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>1.3 Mg CO2/ha/yr</t>
+          <t>1.3 tonnes CO2/ha/yr</t>
         </is>
       </c>
     </row>
@@ -618,7 +772,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>USD 51/Mg CO2</t>
+          <t>USD 51/tonnes CO2</t>
         </is>
       </c>
     </row>
@@ -682,6 +836,8 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
@@ -713,6 +869,7 @@
       </c>
       <c r="B24" s="6" t="n"/>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
@@ -723,7 +880,7 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Mangrove physical (Mg CO2/yr)</t>
+          <t>Mangrove physical (tonnes CO2/yr)</t>
         </is>
       </c>
       <c r="B27" s="6" t="n"/>
@@ -739,7 +896,7 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Seagrass physical (Mg CO2/yr)</t>
+          <t>Seagrass physical (tonnes CO2/yr)</t>
         </is>
       </c>
       <c r="B29" s="6" t="n"/>
@@ -760,6 +917,7 @@
       </c>
       <c r="B31" s="6" t="n"/>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
@@ -775,6 +933,7 @@
       </c>
       <c r="B34" s="6" t="n"/>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
@@ -803,7 +962,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00006100"/>
@@ -824,6 +983,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -847,7 +1007,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Mangrove carbon (Mg CO2/yr)</t>
+          <t>Mangrove carbon (tonnes CO2/yr)</t>
         </is>
       </c>
       <c r="B5" s="7" t="n">
@@ -867,7 +1027,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Seagrass carbon (Mg CO2/yr)</t>
+          <t>Seagrass carbon (tonnes CO2/yr)</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
@@ -926,7 +1086,6 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -937,6 +1096,504 @@
       <c r="B14" s="7" t="n">
         <v>2804085</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="003B9C7B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Glossary of Terms and Abbreviations</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Term / Abbreviation</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Full Name</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>GVA</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Gross Value Added</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Total output minus intermediate consumption. The value an industry adds to the economy.</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Currency (e.g., USD, local currency)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>GDP</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Total value of goods and services produced in a country. Sum of GVA across all industries plus taxes minus subsidies.</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>IC</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Intermediate Consumption</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>The value of goods and services consumed as inputs during production (e.g., fuel, raw materials, purchased services). Does not include fixed assets.</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Gross Output</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Total value of goods and services produced by an industry before deducting input costs. Also called gross sales or turnover.</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>SUT</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Supply-Use Tables</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Statistical tables from the national accounts showing what each industry produces (supply) and what each industry consumes (use). Published by the National Statistical Office.</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>SNA</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>System of National Accounts</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>The international statistical standard for measuring economic activity. Published by the UN. The basis for GDP calculation.</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>SEEA-EA</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>System of Environmental-Economic Accounting - Ecosystem Accounting</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>The international statistical standard for measuring ecosystems, their condition, and the services they provide.</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>OESA</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Ocean Economy Satellite Account</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>A satellite account that reorganizes national accounts to identify the market-based ocean economy. Reports GDP-compatible indicators.</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>OTSA</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Ocean Tourism Satellite Account</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>A satellite account focused on coastal and marine tourism's economic contribution. A subset of OESA.</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Ocean Economy Partial</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>The share (0 to 1) of a mixed industry's output that is ocean-related. For example, if 30% of construction is coastal, the partial is 0.30.</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Proportion (0 to 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>CI</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Condition Index</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>A normalized score from 0 (fully degraded) to 1 (reference/healthy condition). Used in SEEA-EA condition accounts.</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Index (0 to 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>NCP</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Net Carbon Production</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>The rate at which an ecosystem sequesters carbon dioxide per unit area per year.</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Mg CO2/ha/yr</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>SCC</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Social Cost of Carbon</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>An estimate of the economic damage caused by emitting one additional tonne of CO2. Used to value carbon sequestration.</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>USD per Mg CO2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Mg CO2</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Megagrams of CO2</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Metric tonnes of carbon dioxide. 1 Mg = 1 tonne = 1,000 kg.</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>ha</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Hectares</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Unit of area. 1 hectare = 10,000 square metres = 0.01 square kilometres.</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>kg/yr</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Kilograms per year</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Physical quantity measured in kilograms over one year.</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Mass per time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>USD million</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>United States Dollars, millions</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Monetary values expressed in millions of US dollars. For example, USD 132.5 million = USD 132,500,000.</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>R million</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>South African Rand, millions</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Monetary values in the South Africa example are in millions of Rand.</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>ISIC</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>International Standard Industrial Classification</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>The UN classification system for economic activities. Used to map industries to ocean economy groups.</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>SIC</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Standard Industrial Classification</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>National classification system for economic activities. Varies by country but based on ISIC.</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>EEZ</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Exclusive Economic Zone</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Maritime zone extending 200 nautical miles from a country's coastline, within which the country has rights to marine resources.</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Red-Amber-Green</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>A confidence rating system. Green = high confidence (direct evidence). Amber = moderate (proxy data). Red = low (sparse evidence).</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/s-s-event-bogor/sessions/day-2/clinic/services/services_exercise.xlsx
+++ b/s-s-event-bogor/sessions/day-2/clinic/services/services_exercise.xlsx
@@ -13,7 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Step 3 - Valuation Methods" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Step 4 - Monetary Values" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Step 5 - Final Tables" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answers" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Step 6 - Use Tables" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answers" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,7 +27,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -80,8 +81,14 @@
       <color rgb="000A5455"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00404040"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -111,6 +118,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D5F5E3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003B9C7B"/>
+        <bgColor rgb="003B9C7B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000A5455"/>
+        <bgColor rgb="000A5455"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -184,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -258,6 +283,52 @@
     </xf>
     <xf numFmtId="3" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2458,11 +2529,577 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Step 6: Build the Use Tables -- Who Benefits?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="29" t="inlineStr">
+        <is>
+          <t>The supply table (Step 5) shows where services come from. The use table shows who benefits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t>Part 1: Beneficiary Mapping -- Which sectors benefit from each service?</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>Ecosystem service</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="inlineStr">
+        <is>
+          <t>Primary beneficiary sector(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="32" t="inlineStr">
+        <is>
+          <t>Fish provisioning</t>
+        </is>
+      </c>
+      <c r="B8" s="33" t="inlineStr">
+        <is>
+          <t>Fisheries sector</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="32" t="inlineStr">
+        <is>
+          <t>Carbon sequestration</t>
+        </is>
+      </c>
+      <c r="B9" s="33" t="inlineStr">
+        <is>
+          <t>Global community</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="32" t="inlineStr">
+        <is>
+          <t>Coastal protection</t>
+        </is>
+      </c>
+      <c r="B10" s="33" t="inlineStr">
+        <is>
+          <t>Coastal households / Government (split)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="32" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="B11" s="33" t="inlineStr">
+        <is>
+          <t>Tourism sector + Coastal households</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="32" t="inlineStr">
+        <is>
+          <t>Gleaning</t>
+        </is>
+      </c>
+      <c r="B12" s="33" t="inlineStr">
+        <is>
+          <t>Coastal households</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="32" t="inlineStr">
+        <is>
+          <t>Nursery habitat</t>
+        </is>
+      </c>
+      <c r="B13" s="33" t="inlineStr">
+        <is>
+          <t>Fisheries sector (indirect)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="30" t="inlineStr">
+        <is>
+          <t>Part 2: Physical Use Table</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="29" t="inlineStr">
+        <is>
+          <t>Fill in the physical quantities delivered to each beneficiary sector.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="B19" s="31" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="inlineStr">
+        <is>
+          <t>Fisheries sector</t>
+        </is>
+      </c>
+      <c r="D19" s="31" t="inlineStr">
+        <is>
+          <t>Tourism sector</t>
+        </is>
+      </c>
+      <c r="E19" s="31" t="inlineStr">
+        <is>
+          <t>Coastal households</t>
+        </is>
+      </c>
+      <c r="F19" s="31" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="G19" s="31" t="inlineStr">
+        <is>
+          <t>Global community</t>
+        </is>
+      </c>
+      <c r="H19" s="31" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="32" t="inlineStr">
+        <is>
+          <t>Fish provisioning</t>
+        </is>
+      </c>
+      <c r="B20" s="34" t="inlineStr">
+        <is>
+          <t>kg/yr</t>
+        </is>
+      </c>
+      <c r="C20" s="35" t="n"/>
+      <c r="D20" s="35" t="n"/>
+      <c r="E20" s="35" t="n"/>
+      <c r="F20" s="35" t="n"/>
+      <c r="G20" s="35" t="n"/>
+      <c r="H20" s="36">
+        <f>SUM(C20:G20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="32" t="inlineStr">
+        <is>
+          <t>Carbon sequestration</t>
+        </is>
+      </c>
+      <c r="B21" s="34" t="inlineStr">
+        <is>
+          <t>Mg CO2/yr</t>
+        </is>
+      </c>
+      <c r="C21" s="35" t="n"/>
+      <c r="D21" s="35" t="n"/>
+      <c r="E21" s="35" t="n"/>
+      <c r="F21" s="35" t="n"/>
+      <c r="G21" s="35" t="n"/>
+      <c r="H21" s="36">
+        <f>SUM(C21:G21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="32" t="inlineStr">
+        <is>
+          <t>Coastal protection</t>
+        </is>
+      </c>
+      <c r="B22" s="34" t="inlineStr">
+        <is>
+          <t>m coastline</t>
+        </is>
+      </c>
+      <c r="C22" s="35" t="n"/>
+      <c r="D22" s="35" t="n"/>
+      <c r="E22" s="35" t="n"/>
+      <c r="F22" s="35" t="n"/>
+      <c r="G22" s="35" t="n"/>
+      <c r="H22" s="36">
+        <f>SUM(C22:G22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="32" t="inlineStr">
+        <is>
+          <t>Nursery habitat</t>
+        </is>
+      </c>
+      <c r="B23" s="34" t="inlineStr">
+        <is>
+          <t>kg biomass/yr</t>
+        </is>
+      </c>
+      <c r="C23" s="35" t="n"/>
+      <c r="D23" s="35" t="n"/>
+      <c r="E23" s="35" t="n"/>
+      <c r="F23" s="35" t="n"/>
+      <c r="G23" s="35" t="n"/>
+      <c r="H23" s="36">
+        <f>SUM(C23:G23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="32" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="B24" s="34" t="inlineStr">
+        <is>
+          <t>visitors/yr</t>
+        </is>
+      </c>
+      <c r="C24" s="35" t="n"/>
+      <c r="D24" s="35" t="n"/>
+      <c r="E24" s="35" t="n"/>
+      <c r="F24" s="35" t="n"/>
+      <c r="G24" s="35" t="n"/>
+      <c r="H24" s="36">
+        <f>SUM(C24:G24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="32" t="inlineStr">
+        <is>
+          <t>Gleaning</t>
+        </is>
+      </c>
+      <c r="B25" s="34" t="inlineStr">
+        <is>
+          <t>hours/yr</t>
+        </is>
+      </c>
+      <c r="C25" s="35" t="n"/>
+      <c r="D25" s="35" t="n"/>
+      <c r="E25" s="35" t="n"/>
+      <c r="F25" s="35" t="n"/>
+      <c r="G25" s="35" t="n"/>
+      <c r="H25" s="36">
+        <f>SUM(C25:G25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="32" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B26" s="37" t="n"/>
+      <c r="C26" s="36">
+        <f>SUM(C20:C25)</f>
+        <v/>
+      </c>
+      <c r="D26" s="36">
+        <f>SUM(D20:D25)</f>
+        <v/>
+      </c>
+      <c r="E26" s="36">
+        <f>SUM(E20:E25)</f>
+        <v/>
+      </c>
+      <c r="F26" s="36">
+        <f>SUM(F20:F25)</f>
+        <v/>
+      </c>
+      <c r="G26" s="36">
+        <f>SUM(G20:G25)</f>
+        <v/>
+      </c>
+      <c r="H26" s="36">
+        <f>SUM(H20:H25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="30" t="inlineStr">
+        <is>
+          <t>Part 3: Monetary Use Table (USD/yr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="29" t="inlineStr">
+        <is>
+          <t>Fill in the monetary values delivered to each beneficiary sector.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="B32" s="31" t="inlineStr">
+        <is>
+          <t>Valuation method</t>
+        </is>
+      </c>
+      <c r="C32" s="31" t="inlineStr">
+        <is>
+          <t>Fisheries sector</t>
+        </is>
+      </c>
+      <c r="D32" s="31" t="inlineStr">
+        <is>
+          <t>Tourism sector</t>
+        </is>
+      </c>
+      <c r="E32" s="31" t="inlineStr">
+        <is>
+          <t>Coastal households</t>
+        </is>
+      </c>
+      <c r="F32" s="31" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="G32" s="31" t="inlineStr">
+        <is>
+          <t>Global community</t>
+        </is>
+      </c>
+      <c r="H32" s="31" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="32" t="inlineStr">
+        <is>
+          <t>Fish provisioning</t>
+        </is>
+      </c>
+      <c r="B33" s="38" t="n"/>
+      <c r="C33" s="35" t="n"/>
+      <c r="D33" s="35" t="n"/>
+      <c r="E33" s="35" t="n"/>
+      <c r="F33" s="35" t="n"/>
+      <c r="G33" s="35" t="n"/>
+      <c r="H33" s="36">
+        <f>SUM(C33:G33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="32" t="inlineStr">
+        <is>
+          <t>Carbon sequestration</t>
+        </is>
+      </c>
+      <c r="B34" s="38" t="n"/>
+      <c r="C34" s="35" t="n"/>
+      <c r="D34" s="35" t="n"/>
+      <c r="E34" s="35" t="n"/>
+      <c r="F34" s="35" t="n"/>
+      <c r="G34" s="35" t="n"/>
+      <c r="H34" s="36">
+        <f>SUM(C34:G34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="32" t="inlineStr">
+        <is>
+          <t>Coastal protection</t>
+        </is>
+      </c>
+      <c r="B35" s="38" t="n"/>
+      <c r="C35" s="35" t="n"/>
+      <c r="D35" s="35" t="n"/>
+      <c r="E35" s="35" t="n"/>
+      <c r="F35" s="35" t="n"/>
+      <c r="G35" s="35" t="n"/>
+      <c r="H35" s="36">
+        <f>SUM(C35:G35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="32" t="inlineStr">
+        <is>
+          <t>Nursery habitat</t>
+        </is>
+      </c>
+      <c r="B36" s="38" t="n"/>
+      <c r="C36" s="35" t="n"/>
+      <c r="D36" s="35" t="n"/>
+      <c r="E36" s="35" t="n"/>
+      <c r="F36" s="35" t="n"/>
+      <c r="G36" s="35" t="n"/>
+      <c r="H36" s="36">
+        <f>SUM(C36:G36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="32" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="B37" s="38" t="n"/>
+      <c r="C37" s="35" t="n"/>
+      <c r="D37" s="35" t="n"/>
+      <c r="E37" s="35" t="n"/>
+      <c r="F37" s="35" t="n"/>
+      <c r="G37" s="35" t="n"/>
+      <c r="H37" s="36">
+        <f>SUM(C37:G37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="32" t="inlineStr">
+        <is>
+          <t>Gleaning</t>
+        </is>
+      </c>
+      <c r="B38" s="38" t="n"/>
+      <c r="C38" s="35" t="n"/>
+      <c r="D38" s="35" t="n"/>
+      <c r="E38" s="35" t="n"/>
+      <c r="F38" s="35" t="n"/>
+      <c r="G38" s="35" t="n"/>
+      <c r="H38" s="36">
+        <f>SUM(C38:G38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="32" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B39" s="37" t="n"/>
+      <c r="C39" s="36">
+        <f>SUM(C33:C38)</f>
+        <v/>
+      </c>
+      <c r="D39" s="36">
+        <f>SUM(D33:D38)</f>
+        <v/>
+      </c>
+      <c r="E39" s="36">
+        <f>SUM(E33:E38)</f>
+        <v/>
+      </c>
+      <c r="F39" s="36">
+        <f>SUM(F33:F38)</f>
+        <v/>
+      </c>
+      <c r="G39" s="36">
+        <f>SUM(G33:G38)</f>
+        <v/>
+      </c>
+      <c r="H39" s="36">
+        <f>SUM(H33:H38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="30" t="inlineStr">
+        <is>
+          <t>Discussion Questions</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="39" t="inlineStr">
+        <is>
+          <t>Q1: Which sector receives the most value? What does this mean for management?</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="39" t="inlineStr">
+        <is>
+          <t>Q2: Are there equity implications in how benefits are distributed across sectors?</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A17:H17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="000A5455"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:H105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3324,11 +3961,579 @@
       <c r="E71" s="20" t="n"/>
       <c r="F71" s="21" t="n"/>
     </row>
+    <row r="73">
+      <c r="A73" s="40" t="inlineStr">
+        <is>
+          <t>Step 6: Use Tables -- Answers</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>Beneficiary Mapping:</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>Fish provisioning -&gt; Fisheries sector (they harvest and sell the fish)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>Carbon sequestration -&gt; Global community (climate regulation benefits everyone)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>Coastal protection -&gt; Split between Coastal households (property protection) and Government (infrastructure)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>Nursery habitat -&gt; Fisheries sector (supports fish stocks they depend on)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>Recreation -&gt; Tourism sector (businesses) + Coastal households (local recreation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>Gleaning -&gt; Coastal households (subsistence and supplementary income)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>Physical Use Table (example answers):</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="31" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="B84" s="31" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="C84" s="31" t="inlineStr">
+        <is>
+          <t>Fisheries</t>
+        </is>
+      </c>
+      <c r="D84" s="31" t="inlineStr">
+        <is>
+          <t>Tourism</t>
+        </is>
+      </c>
+      <c r="E84" s="31" t="inlineStr">
+        <is>
+          <t>Coastal HH</t>
+        </is>
+      </c>
+      <c r="F84" s="31" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="G84" s="31" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="H84" s="31" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="41" t="inlineStr">
+        <is>
+          <t>Fish provisioning</t>
+        </is>
+      </c>
+      <c r="B85" s="42" t="inlineStr">
+        <is>
+          <t>kg/yr</t>
+        </is>
+      </c>
+      <c r="C85" s="43" t="n">
+        <v>180000</v>
+      </c>
+      <c r="D85" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="44" t="n">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="41" t="inlineStr">
+        <is>
+          <t>Carbon sequestration</t>
+        </is>
+      </c>
+      <c r="B86" s="42" t="inlineStr">
+        <is>
+          <t>Mg CO2/yr</t>
+        </is>
+      </c>
+      <c r="C86" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="43" t="n">
+        <v>2335</v>
+      </c>
+      <c r="H86" s="44" t="n">
+        <v>2335</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="41" t="inlineStr">
+        <is>
+          <t>Coastal protection</t>
+        </is>
+      </c>
+      <c r="B87" s="42" t="inlineStr">
+        <is>
+          <t>m coastline</t>
+        </is>
+      </c>
+      <c r="C87" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="43" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F87" s="43" t="n">
+        <v>5500</v>
+      </c>
+      <c r="G87" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="44" t="n">
+        <v>15500</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="41" t="inlineStr">
+        <is>
+          <t>Nursery habitat</t>
+        </is>
+      </c>
+      <c r="B88" s="42" t="inlineStr">
+        <is>
+          <t>kg/yr</t>
+        </is>
+      </c>
+      <c r="C88" s="43" t="n">
+        <v>7300</v>
+      </c>
+      <c r="D88" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="44" t="n">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="41" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="B89" s="42" t="inlineStr">
+        <is>
+          <t>visitors/yr</t>
+        </is>
+      </c>
+      <c r="C89" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="43" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E89" s="43" t="n">
+        <v>2400</v>
+      </c>
+      <c r="F89" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="44" t="n">
+        <v>17400</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="41" t="inlineStr">
+        <is>
+          <t>Gleaning</t>
+        </is>
+      </c>
+      <c r="B90" s="42" t="inlineStr">
+        <is>
+          <t>hours/yr</t>
+        </is>
+      </c>
+      <c r="C90" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="43" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F90" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="44" t="n">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>Monetary Use Table (example answers, USD/yr):</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="31" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="B93" s="31" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="C93" s="31" t="inlineStr">
+        <is>
+          <t>Fisheries</t>
+        </is>
+      </c>
+      <c r="D93" s="31" t="inlineStr">
+        <is>
+          <t>Tourism</t>
+        </is>
+      </c>
+      <c r="E93" s="31" t="inlineStr">
+        <is>
+          <t>Coastal HH</t>
+        </is>
+      </c>
+      <c r="F93" s="31" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="G93" s="31" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="H93" s="31" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="41" t="inlineStr">
+        <is>
+          <t>Fish provisioning</t>
+        </is>
+      </c>
+      <c r="B94" s="42" t="inlineStr">
+        <is>
+          <t>Resource rent</t>
+        </is>
+      </c>
+      <c r="C94" s="43" t="n">
+        <v>210000</v>
+      </c>
+      <c r="D94" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="44" t="n">
+        <v>210000</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="41" t="inlineStr">
+        <is>
+          <t>Carbon sequestration</t>
+        </is>
+      </c>
+      <c r="B95" s="42" t="inlineStr">
+        <is>
+          <t>SCC</t>
+        </is>
+      </c>
+      <c r="C95" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="43" t="n">
+        <v>119085</v>
+      </c>
+      <c r="H95" s="44" t="n">
+        <v>119085</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="41" t="inlineStr">
+        <is>
+          <t>Coastal protection</t>
+        </is>
+      </c>
+      <c r="B96" s="42" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="C96" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="43" t="n">
+        <v>880000</v>
+      </c>
+      <c r="F96" s="43" t="n">
+        <v>495000</v>
+      </c>
+      <c r="G96" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="44" t="n">
+        <v>1375000</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="41" t="inlineStr">
+        <is>
+          <t>Nursery habitat</t>
+        </is>
+      </c>
+      <c r="B97" s="42" t="inlineStr">
+        <is>
+          <t>Productivity</t>
+        </is>
+      </c>
+      <c r="C97" s="43" t="n">
+        <v>127750</v>
+      </c>
+      <c r="D97" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="44" t="n">
+        <v>127750</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="41" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="B98" s="42" t="inlineStr">
+        <is>
+          <t>Expenditure</t>
+        </is>
+      </c>
+      <c r="C98" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" s="43" t="n">
+        <v>1275000</v>
+      </c>
+      <c r="E98" s="43" t="n">
+        <v>84000</v>
+      </c>
+      <c r="F98" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="44" t="n">
+        <v>1359000</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="41" t="inlineStr">
+        <is>
+          <t>Gleaning</t>
+        </is>
+      </c>
+      <c r="B99" s="42" t="inlineStr">
+        <is>
+          <t>Equiv. wage</t>
+        </is>
+      </c>
+      <c r="C99" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="43" t="n">
+        <v>63000</v>
+      </c>
+      <c r="F99" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="44" t="n">
+        <v>63000</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="41" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B100" s="37" t="n"/>
+      <c r="C100" s="44" t="n">
+        <v>337750</v>
+      </c>
+      <c r="D100" s="44" t="n">
+        <v>1275000</v>
+      </c>
+      <c r="E100" s="44" t="n">
+        <v>1027000</v>
+      </c>
+      <c r="F100" s="44" t="n">
+        <v>495000</v>
+      </c>
+      <c r="G100" s="44" t="n">
+        <v>119085</v>
+      </c>
+      <c r="H100" s="44" t="n">
+        <v>3253835</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>Discussion Answers:</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="45" t="inlineStr">
+        <is>
+          <t>Q1: Tourism and coastal households receive the most value. Recreation alone generates ~USD 1.36M/yr, and coastal protection adds ~USD 1.38M/yr. This suggests that maintaining healthy coastal ecosystems is economically important for both tourism and residential safety. Management should prioritize habitat integrity for these high-value services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="45" t="inlineStr">
+        <is>
+          <t>Q2: Yes. Fisheries and gleaning communities depend on ecosystem services for livelihoods but receive a smaller share of total monetary value. Carbon sequestration benefits the global community but is valued at only ~USD 119K. Equitable management should consider that subsistence users (gleaners) may be most vulnerable to ecosystem degradation even if their monetary share appears small.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="11">
     <mergeCell ref="B68:F68"/>
+    <mergeCell ref="A92:H92"/>
     <mergeCell ref="B69:F69"/>
+    <mergeCell ref="A83:H83"/>
+    <mergeCell ref="A105:H105"/>
+    <mergeCell ref="A73:H73"/>
+    <mergeCell ref="A103:H103"/>
     <mergeCell ref="B71:F71"/>
+    <mergeCell ref="A102:H102"/>
+    <mergeCell ref="A75:H75"/>
     <mergeCell ref="B70:F70"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/s-s-event-bogor/sessions/day-2/clinic/services/services_exercise.xlsx
+++ b/s-s-event-bogor/sessions/day-2/clinic/services/services_exercise.xlsx
@@ -209,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -330,6 +330,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -696,7 +697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -794,6 +795,41 @@
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>The Answers sheet contains a full answer key so you can check your work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="46" t="inlineStr">
+        <is>
+          <t>Step 6: Build Use Tables (who benefits from each service)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Physical use table: assign quantities to beneficiary sectors</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Monetary use table: assign values to beneficiary sectors</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Sectors: fisheries, tourism, coastal households, government, global community</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - The use table total must match the supply table total</t>
         </is>
       </c>
     </row>
@@ -4530,10 +4566,10 @@
     <mergeCell ref="A83:H83"/>
     <mergeCell ref="A105:H105"/>
     <mergeCell ref="A73:H73"/>
+    <mergeCell ref="B71:F71"/>
     <mergeCell ref="A103:H103"/>
-    <mergeCell ref="B71:F71"/>
+    <mergeCell ref="A75:H75"/>
     <mergeCell ref="A102:H102"/>
-    <mergeCell ref="A75:H75"/>
     <mergeCell ref="B70:F70"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/s-s-event-bogor/sessions/day-2/clinic/services/services_exercise.xlsx
+++ b/s-s-event-bogor/sessions/day-2/clinic/services/services_exercise.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Step 5 - Final Tables" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Step 6 - Use Tables" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answers" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Step 7 - Combined Table" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +28,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -87,8 +88,36 @@
       <color rgb="00404040"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="003B9C7B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00717171"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -136,6 +165,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
         <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002C745B"/>
+        <bgColor rgb="002C745B"/>
       </patternFill>
     </fill>
   </fills>
@@ -209,7 +244,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -331,6 +366,28 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3135,7 +3192,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H105"/>
+  <dimension ref="A1:L129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4555,6 +4612,704 @@
       <c r="A105" s="45" t="inlineStr">
         <is>
           <t>Q2: Yes. Fisheries and gleaning communities depend on ecosystem services for livelihoods but receive a smaller share of total monetary value. Carbon sequestration benefits the global community but is valued at only ~USD 119K. Equitable management should consider that subsistence users (gleaners) may be most vulnerable to ecosystem degradation even if their monetary share appears small.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="40" t="inlineStr">
+        <is>
+          <t>Step 7: Combined Supply and Use Table -- Answers</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="47" t="inlineStr">
+        <is>
+          <t>Physical Combined Supply and Use Table:</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="48" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="B111" s="48" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="C111" s="48" t="inlineStr">
+        <is>
+          <t>Coral reefs</t>
+        </is>
+      </c>
+      <c r="D111" s="48" t="inlineStr">
+        <is>
+          <t>Seagrass</t>
+        </is>
+      </c>
+      <c r="E111" s="48" t="inlineStr">
+        <is>
+          <t>Mangroves</t>
+        </is>
+      </c>
+      <c r="F111" s="48" t="inlineStr">
+        <is>
+          <t>Total supply</t>
+        </is>
+      </c>
+      <c r="G111" s="48" t="inlineStr">
+        <is>
+          <t>Fisheries</t>
+        </is>
+      </c>
+      <c r="H111" s="48" t="inlineStr">
+        <is>
+          <t>Tourism</t>
+        </is>
+      </c>
+      <c r="I111" s="48" t="inlineStr">
+        <is>
+          <t>Coastal HH</t>
+        </is>
+      </c>
+      <c r="J111" s="48" t="inlineStr">
+        <is>
+          <t>Govt</t>
+        </is>
+      </c>
+      <c r="K111" s="48" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="L111" s="48" t="inlineStr">
+        <is>
+          <t>Total use</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="48" t="inlineStr">
+        <is>
+          <t>Fish provisioning</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>kg/yr</t>
+        </is>
+      </c>
+      <c r="C112" s="49" t="n">
+        <v>120000</v>
+      </c>
+      <c r="D112" s="49" t="n">
+        <v>45000</v>
+      </c>
+      <c r="E112" s="49" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F112" s="49" t="n">
+        <v>180000</v>
+      </c>
+      <c r="G112" s="49" t="n">
+        <v>180000</v>
+      </c>
+      <c r="H112" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" s="49" t="n">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="48" t="inlineStr">
+        <is>
+          <t>Carbon sequestration</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>Mg CO2/yr</t>
+        </is>
+      </c>
+      <c r="C113" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="49" t="n">
+        <v>1040</v>
+      </c>
+      <c r="E113" s="49" t="n">
+        <v>1295</v>
+      </c>
+      <c r="F113" s="49" t="n">
+        <v>2335</v>
+      </c>
+      <c r="G113" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" s="49" t="n">
+        <v>2335</v>
+      </c>
+      <c r="L113" s="49" t="n">
+        <v>2335</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="48" t="inlineStr">
+        <is>
+          <t>Coastal protection</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>m coastline</t>
+        </is>
+      </c>
+      <c r="C114" s="49" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D114" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="49" t="n">
+        <v>3500</v>
+      </c>
+      <c r="F114" s="49" t="n">
+        <v>15500</v>
+      </c>
+      <c r="G114" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" s="49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J114" s="49" t="n">
+        <v>5500</v>
+      </c>
+      <c r="K114" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" s="49" t="n">
+        <v>15500</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="48" t="inlineStr">
+        <is>
+          <t>Nursery habitat</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>kg/yr</t>
+        </is>
+      </c>
+      <c r="C115" s="49" t="n">
+        <v>4500</v>
+      </c>
+      <c r="D115" s="49" t="n">
+        <v>2800</v>
+      </c>
+      <c r="E115" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="49" t="n">
+        <v>7300</v>
+      </c>
+      <c r="G115" s="49" t="n">
+        <v>7300</v>
+      </c>
+      <c r="H115" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="49" t="n">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="48" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>visitors/yr</t>
+        </is>
+      </c>
+      <c r="C116" s="49" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D116" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="49" t="n">
+        <v>2400</v>
+      </c>
+      <c r="F116" s="49" t="n">
+        <v>17400</v>
+      </c>
+      <c r="G116" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" s="49" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I116" s="49" t="n">
+        <v>2400</v>
+      </c>
+      <c r="J116" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="49" t="n">
+        <v>17400</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="48" t="inlineStr">
+        <is>
+          <t>Gleaning</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>hours/yr</t>
+        </is>
+      </c>
+      <c r="C117" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="49" t="n">
+        <v>18000</v>
+      </c>
+      <c r="E117" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="49" t="n">
+        <v>18000</v>
+      </c>
+      <c r="G117" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" s="49" t="n">
+        <v>18000</v>
+      </c>
+      <c r="J117" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="49" t="n">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="47" t="inlineStr">
+        <is>
+          <t>Monetary Combined Supply and Use Table (USD/yr):</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="48" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="B120" s="48" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="C120" s="48" t="inlineStr">
+        <is>
+          <t>Coral reefs</t>
+        </is>
+      </c>
+      <c r="D120" s="48" t="inlineStr">
+        <is>
+          <t>Seagrass</t>
+        </is>
+      </c>
+      <c r="E120" s="48" t="inlineStr">
+        <is>
+          <t>Mangroves</t>
+        </is>
+      </c>
+      <c r="F120" s="48" t="inlineStr">
+        <is>
+          <t>Total supply</t>
+        </is>
+      </c>
+      <c r="G120" s="48" t="inlineStr">
+        <is>
+          <t>Fisheries</t>
+        </is>
+      </c>
+      <c r="H120" s="48" t="inlineStr">
+        <is>
+          <t>Tourism</t>
+        </is>
+      </c>
+      <c r="I120" s="48" t="inlineStr">
+        <is>
+          <t>Coastal HH</t>
+        </is>
+      </c>
+      <c r="J120" s="48" t="inlineStr">
+        <is>
+          <t>Govt</t>
+        </is>
+      </c>
+      <c r="K120" s="48" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="L120" s="48" t="inlineStr">
+        <is>
+          <t>Total use</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="48" t="inlineStr">
+        <is>
+          <t>Fish provisioning</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>USD/yr</t>
+        </is>
+      </c>
+      <c r="C121" s="49" t="n">
+        <v>140000</v>
+      </c>
+      <c r="D121" s="49" t="n">
+        <v>52500</v>
+      </c>
+      <c r="E121" s="49" t="n">
+        <v>17500</v>
+      </c>
+      <c r="F121" s="49" t="n">
+        <v>210000</v>
+      </c>
+      <c r="G121" s="49" t="n">
+        <v>210000</v>
+      </c>
+      <c r="H121" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" s="49" t="n">
+        <v>210000</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="48" t="inlineStr">
+        <is>
+          <t>Carbon sequestration</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>USD/yr</t>
+        </is>
+      </c>
+      <c r="C122" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="49" t="n">
+        <v>53040</v>
+      </c>
+      <c r="E122" s="49" t="n">
+        <v>66045</v>
+      </c>
+      <c r="F122" s="49" t="n">
+        <v>119085</v>
+      </c>
+      <c r="G122" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" s="49" t="n">
+        <v>119085</v>
+      </c>
+      <c r="L122" s="49" t="n">
+        <v>119085</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="48" t="inlineStr">
+        <is>
+          <t>Coastal protection</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>USD/yr</t>
+        </is>
+      </c>
+      <c r="C123" s="49" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="D123" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="49" t="n">
+        <v>350000</v>
+      </c>
+      <c r="F123" s="49" t="n">
+        <v>1550000</v>
+      </c>
+      <c r="G123" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" s="49" t="n">
+        <v>880000</v>
+      </c>
+      <c r="J123" s="49" t="n">
+        <v>495000</v>
+      </c>
+      <c r="K123" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" s="49" t="n">
+        <v>1375000</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="48" t="inlineStr">
+        <is>
+          <t>Nursery habitat</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>USD/yr</t>
+        </is>
+      </c>
+      <c r="C124" s="49" t="n">
+        <v>90000</v>
+      </c>
+      <c r="D124" s="49" t="n">
+        <v>56000</v>
+      </c>
+      <c r="E124" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="49" t="n">
+        <v>146000</v>
+      </c>
+      <c r="G124" s="49" t="n">
+        <v>127750</v>
+      </c>
+      <c r="H124" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" s="49" t="n">
+        <v>127750</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="48" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>USD/yr</t>
+        </is>
+      </c>
+      <c r="C125" s="49" t="n">
+        <v>1275000</v>
+      </c>
+      <c r="D125" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="49" t="n">
+        <v>84000</v>
+      </c>
+      <c r="F125" s="49" t="n">
+        <v>1359000</v>
+      </c>
+      <c r="G125" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" s="49" t="n">
+        <v>1275000</v>
+      </c>
+      <c r="I125" s="49" t="n">
+        <v>84000</v>
+      </c>
+      <c r="J125" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" s="49" t="n">
+        <v>1359000</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="48" t="inlineStr">
+        <is>
+          <t>Gleaning</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>USD/yr</t>
+        </is>
+      </c>
+      <c r="C126" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="49" t="n">
+        <v>48000</v>
+      </c>
+      <c r="E126" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="49" t="n">
+        <v>48000</v>
+      </c>
+      <c r="G126" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" s="49" t="n">
+        <v>63000</v>
+      </c>
+      <c r="J126" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="49" t="n">
+        <v>63000</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="48" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>USD/yr</t>
+        </is>
+      </c>
+      <c r="C127" s="49" t="n">
+        <v>2705000</v>
+      </c>
+      <c r="D127" s="49" t="n">
+        <v>209540</v>
+      </c>
+      <c r="E127" s="49" t="n">
+        <v>517545</v>
+      </c>
+      <c r="F127" s="49" t="n">
+        <v>3432085</v>
+      </c>
+      <c r="G127" s="49" t="n">
+        <v>337750</v>
+      </c>
+      <c r="H127" s="49" t="n">
+        <v>1275000</v>
+      </c>
+      <c r="I127" s="49" t="n">
+        <v>1027000</v>
+      </c>
+      <c r="J127" s="49" t="n">
+        <v>495000</v>
+      </c>
+      <c r="K127" s="49" t="n">
+        <v>119085</v>
+      </c>
+      <c r="L127" s="49" t="n">
+        <v>3253835</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="50" t="inlineStr">
+        <is>
+          <t>Key check: For every row, Total supply = Total use. This is the SEEA EA accounting identity.</t>
         </is>
       </c>
     </row>
@@ -4574,4 +5329,515 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="51" t="inlineStr">
+        <is>
+          <t>Step 7: Build the Combined Supply and Use Table</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>The SEEA EA presents supply and use together in a single integrated table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Combine your supply data (Step 2/5) and use data (Step 6) into the table below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="46" t="inlineStr">
+        <is>
+          <t>Check: Total supply = Total use for each service row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="51" t="inlineStr">
+        <is>
+          <t>Physical Combined Supply and Use Table</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="52" t="n"/>
+      <c r="B8" s="52" t="n"/>
+      <c r="C8" s="31" t="inlineStr">
+        <is>
+          <t>SUPPLY (by ecosystem)</t>
+        </is>
+      </c>
+      <c r="D8" s="53" t="n"/>
+      <c r="E8" s="53" t="n"/>
+      <c r="F8" s="53" t="n"/>
+      <c r="G8" s="54" t="inlineStr">
+        <is>
+          <t>USE (by beneficiary)</t>
+        </is>
+      </c>
+      <c r="H8" s="52" t="n"/>
+      <c r="I8" s="52" t="n"/>
+      <c r="J8" s="52" t="n"/>
+      <c r="K8" s="52" t="n"/>
+      <c r="L8" s="52" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="55" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="B9" s="31" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="C9" s="56" t="inlineStr">
+        <is>
+          <t>Coral reefs</t>
+        </is>
+      </c>
+      <c r="D9" s="56" t="inlineStr">
+        <is>
+          <t>Seagrass</t>
+        </is>
+      </c>
+      <c r="E9" s="56" t="inlineStr">
+        <is>
+          <t>Mangroves</t>
+        </is>
+      </c>
+      <c r="F9" s="56" t="inlineStr">
+        <is>
+          <t>Total supply</t>
+        </is>
+      </c>
+      <c r="G9" s="57" t="inlineStr">
+        <is>
+          <t>Fisheries</t>
+        </is>
+      </c>
+      <c r="H9" s="57" t="inlineStr">
+        <is>
+          <t>Tourism</t>
+        </is>
+      </c>
+      <c r="I9" s="57" t="inlineStr">
+        <is>
+          <t>Coastal HH</t>
+        </is>
+      </c>
+      <c r="J9" s="57" t="inlineStr">
+        <is>
+          <t>Govt</t>
+        </is>
+      </c>
+      <c r="K9" s="57" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="L9" s="57" t="inlineStr">
+        <is>
+          <t>Total use</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="32" t="inlineStr">
+        <is>
+          <t>Fish provisioning</t>
+        </is>
+      </c>
+      <c r="B10" s="58" t="inlineStr">
+        <is>
+          <t>kg/yr</t>
+        </is>
+      </c>
+      <c r="C10" s="35" t="n"/>
+      <c r="D10" s="35" t="n"/>
+      <c r="E10" s="35" t="n"/>
+      <c r="F10" s="35" t="n"/>
+      <c r="G10" s="35" t="n"/>
+      <c r="H10" s="35" t="n"/>
+      <c r="I10" s="35" t="n"/>
+      <c r="J10" s="35" t="n"/>
+      <c r="K10" s="35" t="n"/>
+      <c r="L10" s="35" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="32" t="inlineStr">
+        <is>
+          <t>Carbon sequestration</t>
+        </is>
+      </c>
+      <c r="B11" s="58" t="inlineStr">
+        <is>
+          <t>Mg CO2/yr</t>
+        </is>
+      </c>
+      <c r="C11" s="35" t="n"/>
+      <c r="D11" s="35" t="n"/>
+      <c r="E11" s="35" t="n"/>
+      <c r="F11" s="35" t="n"/>
+      <c r="G11" s="35" t="n"/>
+      <c r="H11" s="35" t="n"/>
+      <c r="I11" s="35" t="n"/>
+      <c r="J11" s="35" t="n"/>
+      <c r="K11" s="35" t="n"/>
+      <c r="L11" s="35" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="32" t="inlineStr">
+        <is>
+          <t>Coastal protection</t>
+        </is>
+      </c>
+      <c r="B12" s="58" t="inlineStr">
+        <is>
+          <t>m coastline</t>
+        </is>
+      </c>
+      <c r="C12" s="35" t="n"/>
+      <c r="D12" s="35" t="n"/>
+      <c r="E12" s="35" t="n"/>
+      <c r="F12" s="35" t="n"/>
+      <c r="G12" s="35" t="n"/>
+      <c r="H12" s="35" t="n"/>
+      <c r="I12" s="35" t="n"/>
+      <c r="J12" s="35" t="n"/>
+      <c r="K12" s="35" t="n"/>
+      <c r="L12" s="35" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="32" t="inlineStr">
+        <is>
+          <t>Nursery habitat</t>
+        </is>
+      </c>
+      <c r="B13" s="58" t="inlineStr">
+        <is>
+          <t>kg/yr</t>
+        </is>
+      </c>
+      <c r="C13" s="35" t="n"/>
+      <c r="D13" s="35" t="n"/>
+      <c r="E13" s="35" t="n"/>
+      <c r="F13" s="35" t="n"/>
+      <c r="G13" s="35" t="n"/>
+      <c r="H13" s="35" t="n"/>
+      <c r="I13" s="35" t="n"/>
+      <c r="J13" s="35" t="n"/>
+      <c r="K13" s="35" t="n"/>
+      <c r="L13" s="35" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="32" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="B14" s="58" t="inlineStr">
+        <is>
+          <t>visitors/yr</t>
+        </is>
+      </c>
+      <c r="C14" s="35" t="n"/>
+      <c r="D14" s="35" t="n"/>
+      <c r="E14" s="35" t="n"/>
+      <c r="F14" s="35" t="n"/>
+      <c r="G14" s="35" t="n"/>
+      <c r="H14" s="35" t="n"/>
+      <c r="I14" s="35" t="n"/>
+      <c r="J14" s="35" t="n"/>
+      <c r="K14" s="35" t="n"/>
+      <c r="L14" s="35" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="32" t="inlineStr">
+        <is>
+          <t>Gleaning</t>
+        </is>
+      </c>
+      <c r="B15" s="58" t="inlineStr">
+        <is>
+          <t>hours/yr</t>
+        </is>
+      </c>
+      <c r="C15" s="35" t="n"/>
+      <c r="D15" s="35" t="n"/>
+      <c r="E15" s="35" t="n"/>
+      <c r="F15" s="35" t="n"/>
+      <c r="G15" s="35" t="n"/>
+      <c r="H15" s="35" t="n"/>
+      <c r="I15" s="35" t="n"/>
+      <c r="J15" s="35" t="n"/>
+      <c r="K15" s="35" t="n"/>
+      <c r="L15" s="35" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="51" t="inlineStr">
+        <is>
+          <t>Monetary Combined Supply and Use Table (USD/yr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="52" t="n"/>
+      <c r="B19" s="52" t="n"/>
+      <c r="C19" s="31" t="inlineStr">
+        <is>
+          <t>SUPPLY (by ecosystem)</t>
+        </is>
+      </c>
+      <c r="D19" s="53" t="n"/>
+      <c r="E19" s="53" t="n"/>
+      <c r="F19" s="53" t="n"/>
+      <c r="G19" s="54" t="inlineStr">
+        <is>
+          <t>USE (by beneficiary)</t>
+        </is>
+      </c>
+      <c r="H19" s="52" t="n"/>
+      <c r="I19" s="52" t="n"/>
+      <c r="J19" s="52" t="n"/>
+      <c r="K19" s="52" t="n"/>
+      <c r="L19" s="52" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="55" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="B20" s="31" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="C20" s="56" t="inlineStr">
+        <is>
+          <t>Coral reefs</t>
+        </is>
+      </c>
+      <c r="D20" s="56" t="inlineStr">
+        <is>
+          <t>Seagrass</t>
+        </is>
+      </c>
+      <c r="E20" s="56" t="inlineStr">
+        <is>
+          <t>Mangroves</t>
+        </is>
+      </c>
+      <c r="F20" s="56" t="inlineStr">
+        <is>
+          <t>Total supply</t>
+        </is>
+      </c>
+      <c r="G20" s="57" t="inlineStr">
+        <is>
+          <t>Fisheries</t>
+        </is>
+      </c>
+      <c r="H20" s="57" t="inlineStr">
+        <is>
+          <t>Tourism</t>
+        </is>
+      </c>
+      <c r="I20" s="57" t="inlineStr">
+        <is>
+          <t>Coastal HH</t>
+        </is>
+      </c>
+      <c r="J20" s="57" t="inlineStr">
+        <is>
+          <t>Govt</t>
+        </is>
+      </c>
+      <c r="K20" s="57" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="L20" s="57" t="inlineStr">
+        <is>
+          <t>Total use</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="32" t="inlineStr">
+        <is>
+          <t>Fish provisioning</t>
+        </is>
+      </c>
+      <c r="B21" s="58" t="inlineStr">
+        <is>
+          <t>USD/yr</t>
+        </is>
+      </c>
+      <c r="C21" s="35" t="n"/>
+      <c r="D21" s="35" t="n"/>
+      <c r="E21" s="35" t="n"/>
+      <c r="F21" s="35" t="n"/>
+      <c r="G21" s="35" t="n"/>
+      <c r="H21" s="35" t="n"/>
+      <c r="I21" s="35" t="n"/>
+      <c r="J21" s="35" t="n"/>
+      <c r="K21" s="35" t="n"/>
+      <c r="L21" s="35" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="32" t="inlineStr">
+        <is>
+          <t>Carbon sequestration</t>
+        </is>
+      </c>
+      <c r="B22" s="58" t="inlineStr">
+        <is>
+          <t>USD/yr</t>
+        </is>
+      </c>
+      <c r="C22" s="35" t="n"/>
+      <c r="D22" s="35" t="n"/>
+      <c r="E22" s="35" t="n"/>
+      <c r="F22" s="35" t="n"/>
+      <c r="G22" s="35" t="n"/>
+      <c r="H22" s="35" t="n"/>
+      <c r="I22" s="35" t="n"/>
+      <c r="J22" s="35" t="n"/>
+      <c r="K22" s="35" t="n"/>
+      <c r="L22" s="35" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="32" t="inlineStr">
+        <is>
+          <t>Coastal protection</t>
+        </is>
+      </c>
+      <c r="B23" s="58" t="inlineStr">
+        <is>
+          <t>USD/yr</t>
+        </is>
+      </c>
+      <c r="C23" s="35" t="n"/>
+      <c r="D23" s="35" t="n"/>
+      <c r="E23" s="35" t="n"/>
+      <c r="F23" s="35" t="n"/>
+      <c r="G23" s="35" t="n"/>
+      <c r="H23" s="35" t="n"/>
+      <c r="I23" s="35" t="n"/>
+      <c r="J23" s="35" t="n"/>
+      <c r="K23" s="35" t="n"/>
+      <c r="L23" s="35" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="32" t="inlineStr">
+        <is>
+          <t>Nursery habitat</t>
+        </is>
+      </c>
+      <c r="B24" s="58" t="inlineStr">
+        <is>
+          <t>USD/yr</t>
+        </is>
+      </c>
+      <c r="C24" s="35" t="n"/>
+      <c r="D24" s="35" t="n"/>
+      <c r="E24" s="35" t="n"/>
+      <c r="F24" s="35" t="n"/>
+      <c r="G24" s="35" t="n"/>
+      <c r="H24" s="35" t="n"/>
+      <c r="I24" s="35" t="n"/>
+      <c r="J24" s="35" t="n"/>
+      <c r="K24" s="35" t="n"/>
+      <c r="L24" s="35" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="32" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="B25" s="58" t="inlineStr">
+        <is>
+          <t>USD/yr</t>
+        </is>
+      </c>
+      <c r="C25" s="35" t="n"/>
+      <c r="D25" s="35" t="n"/>
+      <c r="E25" s="35" t="n"/>
+      <c r="F25" s="35" t="n"/>
+      <c r="G25" s="35" t="n"/>
+      <c r="H25" s="35" t="n"/>
+      <c r="I25" s="35" t="n"/>
+      <c r="J25" s="35" t="n"/>
+      <c r="K25" s="35" t="n"/>
+      <c r="L25" s="35" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="32" t="inlineStr">
+        <is>
+          <t>Gleaning</t>
+        </is>
+      </c>
+      <c r="B26" s="58" t="inlineStr">
+        <is>
+          <t>USD/yr</t>
+        </is>
+      </c>
+      <c r="C26" s="35" t="n"/>
+      <c r="D26" s="35" t="n"/>
+      <c r="E26" s="35" t="n"/>
+      <c r="F26" s="35" t="n"/>
+      <c r="G26" s="35" t="n"/>
+      <c r="H26" s="35" t="n"/>
+      <c r="I26" s="35" t="n"/>
+      <c r="J26" s="35" t="n"/>
+      <c r="K26" s="35" t="n"/>
+      <c r="L26" s="35" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A7:L7"/>
+    <mergeCell ref="G19:L19"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="G8:L8"/>
+    <mergeCell ref="A18:L18"/>
+    <mergeCell ref="C19:F19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/s-s-event-bogor/sessions/day-2/clinic/services/services_exercise.xlsx
+++ b/s-s-event-bogor/sessions/day-2/clinic/services/services_exercise.xlsx
@@ -28,7 +28,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -116,8 +116,44 @@
       <color rgb="00717171"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="00404040"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00404040"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00404040"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -171,6 +207,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="002C745B"/>
         <bgColor rgb="002C745B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5E8D4"/>
+        <bgColor rgb="00D5E8D4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B2D8D8"/>
+        <bgColor rgb="00B2D8D8"/>
       </patternFill>
     </fill>
   </fills>
@@ -244,7 +292,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -387,6 +435,50 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5337,506 +5429,662 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="51" t="inlineStr">
-        <is>
-          <t>Step 7: Build the Combined Supply and Use Table</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>The SEEA EA presents supply and use together in a single integrated table.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Combine your supply data (Step 2/5) and use data (Step 6) into the table below.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="46" t="inlineStr">
-        <is>
-          <t>Check: Total supply = Total use for each service row.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="51" t="inlineStr">
-        <is>
-          <t>Physical Combined Supply and Use Table</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="52" t="n"/>
-      <c r="B8" s="52" t="n"/>
-      <c r="C8" s="31" t="inlineStr">
-        <is>
-          <t>SUPPLY (by ecosystem)</t>
-        </is>
-      </c>
-      <c r="D8" s="53" t="n"/>
-      <c r="E8" s="53" t="n"/>
-      <c r="F8" s="53" t="n"/>
-      <c r="G8" s="54" t="inlineStr">
-        <is>
-          <t>USE (by beneficiary)</t>
-        </is>
-      </c>
-      <c r="H8" s="52" t="n"/>
-      <c r="I8" s="52" t="n"/>
-      <c r="J8" s="52" t="n"/>
-      <c r="K8" s="52" t="n"/>
-      <c r="L8" s="52" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="55" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="59" t="inlineStr">
+        <is>
+          <t>SUPPLY TABLE (Table 7.1a)</t>
+        </is>
+      </c>
+      <c r="B1" s="60" t="n"/>
+      <c r="C1" s="60" t="n"/>
+      <c r="D1" s="60" t="n"/>
+      <c r="E1" s="60" t="n"/>
+      <c r="F1" s="60" t="n"/>
+      <c r="G1" s="60" t="n"/>
+      <c r="H1" s="60" t="n"/>
+      <c r="I1" s="60" t="n"/>
+      <c r="J1" s="60" t="n"/>
+      <c r="K1" s="60" t="n"/>
+      <c r="L1" s="60" t="n"/>
+      <c r="M1" s="60" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="53" t="n"/>
+      <c r="B2" s="53" t="n"/>
+      <c r="C2" s="61" t="inlineStr">
+        <is>
+          <t>Economic units</t>
+        </is>
+      </c>
+      <c r="D2" s="53" t="n"/>
+      <c r="E2" s="53" t="n"/>
+      <c r="F2" s="53" t="n"/>
+      <c r="G2" s="53" t="n"/>
+      <c r="H2" s="53" t="n"/>
+      <c r="I2" s="61" t="inlineStr">
+        <is>
+          <t>Ecosystem types</t>
+        </is>
+      </c>
+      <c r="J2" s="53" t="n"/>
+      <c r="K2" s="53" t="n"/>
+      <c r="L2" s="53" t="n"/>
+      <c r="M2" s="53" t="n"/>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" s="62" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="B9" s="31" t="inlineStr">
+      <c r="B3" s="62" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="C9" s="56" t="inlineStr">
-        <is>
-          <t>Coral reefs</t>
-        </is>
-      </c>
-      <c r="D9" s="56" t="inlineStr">
-        <is>
-          <t>Seagrass</t>
-        </is>
-      </c>
-      <c r="E9" s="56" t="inlineStr">
-        <is>
-          <t>Mangroves</t>
-        </is>
-      </c>
-      <c r="F9" s="56" t="inlineStr">
-        <is>
-          <t>Total supply</t>
-        </is>
-      </c>
-      <c r="G9" s="57" t="inlineStr">
+      <c r="C3" s="62" t="inlineStr">
         <is>
           <t>Fisheries</t>
         </is>
       </c>
-      <c r="H9" s="57" t="inlineStr">
+      <c r="D3" s="62" t="inlineStr">
         <is>
           <t>Tourism</t>
         </is>
       </c>
-      <c r="I9" s="57" t="inlineStr">
-        <is>
-          <t>Coastal HH</t>
-        </is>
-      </c>
-      <c r="J9" s="57" t="inlineStr">
+      <c r="E3" s="62" t="inlineStr">
+        <is>
+          <t>Other industry</t>
+        </is>
+      </c>
+      <c r="F3" s="62" t="inlineStr">
+        <is>
+          <t>Households</t>
+        </is>
+      </c>
+      <c r="G3" s="62" t="inlineStr">
         <is>
           <t>Govt</t>
         </is>
       </c>
-      <c r="K9" s="57" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="L9" s="57" t="inlineStr">
-        <is>
-          <t>Total use</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="H3" s="62" t="inlineStr">
+        <is>
+          <t>Global/Exports</t>
+        </is>
+      </c>
+      <c r="I3" s="62" t="inlineStr">
+        <is>
+          <t>Coral reefs
+(M1.3)</t>
+        </is>
+      </c>
+      <c r="J3" s="62" t="inlineStr">
+        <is>
+          <t>Seagrass meadows
+(M1.1)</t>
+        </is>
+      </c>
+      <c r="K3" s="62" t="inlineStr">
+        <is>
+          <t>Mangroves
+(MFT1.2)</t>
+        </is>
+      </c>
+      <c r="L3" s="62" t="inlineStr">
+        <is>
+          <t>Total ecosystem</t>
+        </is>
+      </c>
+      <c r="M3" s="62" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="63" t="inlineStr">
+        <is>
+          <t>Provisioning services (SEEA EA 6.1)</t>
+        </is>
+      </c>
+      <c r="B4" s="64" t="n"/>
+      <c r="C4" s="64" t="n"/>
+      <c r="D4" s="64" t="n"/>
+      <c r="E4" s="64" t="n"/>
+      <c r="F4" s="64" t="n"/>
+      <c r="G4" s="64" t="n"/>
+      <c r="H4" s="64" t="n"/>
+      <c r="I4" s="64" t="n"/>
+      <c r="J4" s="64" t="n"/>
+      <c r="K4" s="64" t="n"/>
+      <c r="L4" s="64" t="n"/>
+      <c r="M4" s="64" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="65" t="inlineStr">
         <is>
           <t>Fish provisioning</t>
         </is>
       </c>
-      <c r="B10" s="58" t="inlineStr">
+      <c r="B5" s="66" t="inlineStr">
         <is>
           <t>kg/yr</t>
         </is>
       </c>
-      <c r="C10" s="35" t="n"/>
-      <c r="D10" s="35" t="n"/>
-      <c r="E10" s="35" t="n"/>
-      <c r="F10" s="35" t="n"/>
-      <c r="G10" s="35" t="n"/>
-      <c r="H10" s="35" t="n"/>
-      <c r="I10" s="35" t="n"/>
-      <c r="J10" s="35" t="n"/>
-      <c r="K10" s="35" t="n"/>
-      <c r="L10" s="35" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="32" t="inlineStr">
+      <c r="C5" s="67" t="n"/>
+      <c r="D5" s="67" t="n"/>
+      <c r="E5" s="67" t="n"/>
+      <c r="F5" s="67" t="n"/>
+      <c r="G5" s="67" t="n"/>
+      <c r="H5" s="67" t="n"/>
+      <c r="I5" s="68" t="n"/>
+      <c r="J5" s="68" t="n"/>
+      <c r="K5" s="68" t="n"/>
+      <c r="L5" s="68" t="n"/>
+      <c r="M5" s="68" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="63" t="inlineStr">
+        <is>
+          <t>Regulating &amp; maintenance services (SEEA EA 6.2-6.5)</t>
+        </is>
+      </c>
+      <c r="B6" s="64" t="n"/>
+      <c r="C6" s="64" t="n"/>
+      <c r="D6" s="64" t="n"/>
+      <c r="E6" s="64" t="n"/>
+      <c r="F6" s="64" t="n"/>
+      <c r="G6" s="64" t="n"/>
+      <c r="H6" s="64" t="n"/>
+      <c r="I6" s="64" t="n"/>
+      <c r="J6" s="64" t="n"/>
+      <c r="K6" s="64" t="n"/>
+      <c r="L6" s="64" t="n"/>
+      <c r="M6" s="64" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="65" t="inlineStr">
         <is>
           <t>Carbon sequestration</t>
         </is>
       </c>
-      <c r="B11" s="58" t="inlineStr">
-        <is>
-          <t>Mg CO2/yr</t>
-        </is>
-      </c>
-      <c r="C11" s="35" t="n"/>
-      <c r="D11" s="35" t="n"/>
-      <c r="E11" s="35" t="n"/>
-      <c r="F11" s="35" t="n"/>
-      <c r="G11" s="35" t="n"/>
-      <c r="H11" s="35" t="n"/>
-      <c r="I11" s="35" t="n"/>
-      <c r="J11" s="35" t="n"/>
-      <c r="K11" s="35" t="n"/>
-      <c r="L11" s="35" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="32" t="inlineStr">
+      <c r="B7" s="66" t="inlineStr">
+        <is>
+          <t>Mg CO₂/yr</t>
+        </is>
+      </c>
+      <c r="C7" s="67" t="n"/>
+      <c r="D7" s="67" t="n"/>
+      <c r="E7" s="67" t="n"/>
+      <c r="F7" s="67" t="n"/>
+      <c r="G7" s="67" t="n"/>
+      <c r="H7" s="67" t="n"/>
+      <c r="I7" s="68" t="n"/>
+      <c r="J7" s="68" t="n"/>
+      <c r="K7" s="68" t="n"/>
+      <c r="L7" s="68" t="n"/>
+      <c r="M7" s="68" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="65" t="inlineStr">
         <is>
           <t>Coastal protection</t>
         </is>
       </c>
-      <c r="B12" s="58" t="inlineStr">
-        <is>
-          <t>m coastline</t>
-        </is>
-      </c>
-      <c r="C12" s="35" t="n"/>
-      <c r="D12" s="35" t="n"/>
-      <c r="E12" s="35" t="n"/>
-      <c r="F12" s="35" t="n"/>
-      <c r="G12" s="35" t="n"/>
-      <c r="H12" s="35" t="n"/>
-      <c r="I12" s="35" t="n"/>
-      <c r="J12" s="35" t="n"/>
-      <c r="K12" s="35" t="n"/>
-      <c r="L12" s="35" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="32" t="inlineStr">
-        <is>
-          <t>Nursery habitat</t>
-        </is>
-      </c>
-      <c r="B13" s="58" t="inlineStr">
+      <c r="B8" s="66" t="inlineStr">
+        <is>
+          <t>m of coastline</t>
+        </is>
+      </c>
+      <c r="C8" s="67" t="n"/>
+      <c r="D8" s="67" t="n"/>
+      <c r="E8" s="67" t="n"/>
+      <c r="F8" s="67" t="n"/>
+      <c r="G8" s="67" t="n"/>
+      <c r="H8" s="67" t="n"/>
+      <c r="I8" s="68" t="n"/>
+      <c r="J8" s="68" t="n"/>
+      <c r="K8" s="68" t="n"/>
+      <c r="L8" s="68" t="n"/>
+      <c r="M8" s="68" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="65" t="inlineStr">
+        <is>
+          <t>Nursery habitat support</t>
+        </is>
+      </c>
+      <c r="B9" s="66" t="inlineStr">
+        <is>
+          <t>kg fish/yr</t>
+        </is>
+      </c>
+      <c r="C9" s="67" t="n"/>
+      <c r="D9" s="67" t="n"/>
+      <c r="E9" s="67" t="n"/>
+      <c r="F9" s="67" t="n"/>
+      <c r="G9" s="67" t="n"/>
+      <c r="H9" s="67" t="n"/>
+      <c r="I9" s="68" t="n"/>
+      <c r="J9" s="68" t="n"/>
+      <c r="K9" s="68" t="n"/>
+      <c r="L9" s="68" t="n"/>
+      <c r="M9" s="68" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="63" t="inlineStr">
+        <is>
+          <t>Cultural services (SEEA EA 6.6)</t>
+        </is>
+      </c>
+      <c r="B10" s="64" t="n"/>
+      <c r="C10" s="64" t="n"/>
+      <c r="D10" s="64" t="n"/>
+      <c r="E10" s="64" t="n"/>
+      <c r="F10" s="64" t="n"/>
+      <c r="G10" s="64" t="n"/>
+      <c r="H10" s="64" t="n"/>
+      <c r="I10" s="64" t="n"/>
+      <c r="J10" s="64" t="n"/>
+      <c r="K10" s="64" t="n"/>
+      <c r="L10" s="64" t="n"/>
+      <c r="M10" s="64" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="65" t="inlineStr">
+        <is>
+          <t>Recreation &amp; tourism</t>
+        </is>
+      </c>
+      <c r="B11" s="66" t="inlineStr">
+        <is>
+          <t>visitors/yr</t>
+        </is>
+      </c>
+      <c r="C11" s="67" t="n"/>
+      <c r="D11" s="67" t="n"/>
+      <c r="E11" s="67" t="n"/>
+      <c r="F11" s="67" t="n"/>
+      <c r="G11" s="67" t="n"/>
+      <c r="H11" s="67" t="n"/>
+      <c r="I11" s="68" t="n"/>
+      <c r="J11" s="68" t="n"/>
+      <c r="K11" s="68" t="n"/>
+      <c r="L11" s="68" t="n"/>
+      <c r="M11" s="68" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="65" t="inlineStr">
+        <is>
+          <t>Gleaning (subsistence harvest)</t>
+        </is>
+      </c>
+      <c r="B12" s="66" t="inlineStr">
+        <is>
+          <t>hours/yr</t>
+        </is>
+      </c>
+      <c r="C12" s="67" t="n"/>
+      <c r="D12" s="67" t="n"/>
+      <c r="E12" s="67" t="n"/>
+      <c r="F12" s="67" t="n"/>
+      <c r="G12" s="67" t="n"/>
+      <c r="H12" s="67" t="n"/>
+      <c r="I12" s="68" t="n"/>
+      <c r="J12" s="68" t="n"/>
+      <c r="K12" s="68" t="n"/>
+      <c r="L12" s="68" t="n"/>
+      <c r="M12" s="68" t="n"/>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="69" t="inlineStr">
+        <is>
+          <t>USE TABLE (Table 7.1b)</t>
+        </is>
+      </c>
+      <c r="B14" s="70" t="n"/>
+      <c r="C14" s="70" t="n"/>
+      <c r="D14" s="70" t="n"/>
+      <c r="E14" s="70" t="n"/>
+      <c r="F14" s="70" t="n"/>
+      <c r="G14" s="70" t="n"/>
+      <c r="H14" s="70" t="n"/>
+      <c r="I14" s="70" t="n"/>
+      <c r="J14" s="70" t="n"/>
+      <c r="K14" s="70" t="n"/>
+      <c r="L14" s="70" t="n"/>
+      <c r="M14" s="70" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="71" t="n"/>
+      <c r="B15" s="71" t="n"/>
+      <c r="C15" s="72" t="inlineStr">
+        <is>
+          <t>Economic units</t>
+        </is>
+      </c>
+      <c r="D15" s="71" t="n"/>
+      <c r="E15" s="71" t="n"/>
+      <c r="F15" s="71" t="n"/>
+      <c r="G15" s="71" t="n"/>
+      <c r="H15" s="71" t="n"/>
+      <c r="I15" s="72" t="inlineStr">
+        <is>
+          <t>Ecosystem types</t>
+        </is>
+      </c>
+      <c r="J15" s="71" t="n"/>
+      <c r="K15" s="71" t="n"/>
+      <c r="L15" s="71" t="n"/>
+      <c r="M15" s="71" t="n"/>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="73" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="B16" s="73" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="C16" s="73" t="inlineStr">
+        <is>
+          <t>Fisheries</t>
+        </is>
+      </c>
+      <c r="D16" s="73" t="inlineStr">
+        <is>
+          <t>Tourism</t>
+        </is>
+      </c>
+      <c r="E16" s="73" t="inlineStr">
+        <is>
+          <t>Other industry</t>
+        </is>
+      </c>
+      <c r="F16" s="73" t="inlineStr">
+        <is>
+          <t>Households</t>
+        </is>
+      </c>
+      <c r="G16" s="73" t="inlineStr">
+        <is>
+          <t>Govt</t>
+        </is>
+      </c>
+      <c r="H16" s="73" t="inlineStr">
+        <is>
+          <t>Global/Exports</t>
+        </is>
+      </c>
+      <c r="I16" s="73" t="inlineStr">
+        <is>
+          <t>Coral reefs
+(M1.3)</t>
+        </is>
+      </c>
+      <c r="J16" s="73" t="inlineStr">
+        <is>
+          <t>Seagrass meadows
+(M1.1)</t>
+        </is>
+      </c>
+      <c r="K16" s="73" t="inlineStr">
+        <is>
+          <t>Mangroves
+(MFT1.2)</t>
+        </is>
+      </c>
+      <c r="L16" s="73" t="inlineStr">
+        <is>
+          <t>Total ecosystem</t>
+        </is>
+      </c>
+      <c r="M16" s="73" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="74" t="inlineStr">
+        <is>
+          <t>Provisioning services (SEEA EA 6.1)</t>
+        </is>
+      </c>
+      <c r="B17" s="75" t="n"/>
+      <c r="C17" s="75" t="n"/>
+      <c r="D17" s="75" t="n"/>
+      <c r="E17" s="75" t="n"/>
+      <c r="F17" s="75" t="n"/>
+      <c r="G17" s="75" t="n"/>
+      <c r="H17" s="75" t="n"/>
+      <c r="I17" s="75" t="n"/>
+      <c r="J17" s="75" t="n"/>
+      <c r="K17" s="75" t="n"/>
+      <c r="L17" s="75" t="n"/>
+      <c r="M17" s="75" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="65" t="inlineStr">
+        <is>
+          <t>Fish provisioning</t>
+        </is>
+      </c>
+      <c r="B18" s="66" t="inlineStr">
         <is>
           <t>kg/yr</t>
         </is>
       </c>
-      <c r="C13" s="35" t="n"/>
-      <c r="D13" s="35" t="n"/>
-      <c r="E13" s="35" t="n"/>
-      <c r="F13" s="35" t="n"/>
-      <c r="G13" s="35" t="n"/>
-      <c r="H13" s="35" t="n"/>
-      <c r="I13" s="35" t="n"/>
-      <c r="J13" s="35" t="n"/>
-      <c r="K13" s="35" t="n"/>
-      <c r="L13" s="35" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="32" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
-      <c r="B14" s="58" t="inlineStr">
+      <c r="C18" s="68" t="n"/>
+      <c r="D18" s="68" t="n"/>
+      <c r="E18" s="68" t="n"/>
+      <c r="F18" s="68" t="n"/>
+      <c r="G18" s="68" t="n"/>
+      <c r="H18" s="68" t="n"/>
+      <c r="I18" s="67" t="n"/>
+      <c r="J18" s="67" t="n"/>
+      <c r="K18" s="67" t="n"/>
+      <c r="L18" s="68" t="n"/>
+      <c r="M18" s="68" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="74" t="inlineStr">
+        <is>
+          <t>Regulating &amp; maintenance services (SEEA EA 6.2-6.5)</t>
+        </is>
+      </c>
+      <c r="B19" s="75" t="n"/>
+      <c r="C19" s="75" t="n"/>
+      <c r="D19" s="75" t="n"/>
+      <c r="E19" s="75" t="n"/>
+      <c r="F19" s="75" t="n"/>
+      <c r="G19" s="75" t="n"/>
+      <c r="H19" s="75" t="n"/>
+      <c r="I19" s="75" t="n"/>
+      <c r="J19" s="75" t="n"/>
+      <c r="K19" s="75" t="n"/>
+      <c r="L19" s="75" t="n"/>
+      <c r="M19" s="75" t="n"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="65" t="inlineStr">
+        <is>
+          <t>Carbon sequestration</t>
+        </is>
+      </c>
+      <c r="B20" s="66" t="inlineStr">
+        <is>
+          <t>Mg CO₂/yr</t>
+        </is>
+      </c>
+      <c r="C20" s="68" t="n"/>
+      <c r="D20" s="68" t="n"/>
+      <c r="E20" s="68" t="n"/>
+      <c r="F20" s="68" t="n"/>
+      <c r="G20" s="68" t="n"/>
+      <c r="H20" s="68" t="n"/>
+      <c r="I20" s="67" t="n"/>
+      <c r="J20" s="67" t="n"/>
+      <c r="K20" s="67" t="n"/>
+      <c r="L20" s="68" t="n"/>
+      <c r="M20" s="68" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="65" t="inlineStr">
+        <is>
+          <t>Coastal protection</t>
+        </is>
+      </c>
+      <c r="B21" s="66" t="inlineStr">
+        <is>
+          <t>m of coastline</t>
+        </is>
+      </c>
+      <c r="C21" s="68" t="n"/>
+      <c r="D21" s="68" t="n"/>
+      <c r="E21" s="68" t="n"/>
+      <c r="F21" s="68" t="n"/>
+      <c r="G21" s="68" t="n"/>
+      <c r="H21" s="68" t="n"/>
+      <c r="I21" s="67" t="n"/>
+      <c r="J21" s="67" t="n"/>
+      <c r="K21" s="67" t="n"/>
+      <c r="L21" s="68" t="n"/>
+      <c r="M21" s="68" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="65" t="inlineStr">
+        <is>
+          <t>Nursery habitat support</t>
+        </is>
+      </c>
+      <c r="B22" s="66" t="inlineStr">
+        <is>
+          <t>kg fish/yr</t>
+        </is>
+      </c>
+      <c r="C22" s="68" t="n"/>
+      <c r="D22" s="68" t="n"/>
+      <c r="E22" s="68" t="n"/>
+      <c r="F22" s="68" t="n"/>
+      <c r="G22" s="68" t="n"/>
+      <c r="H22" s="68" t="n"/>
+      <c r="I22" s="67" t="n"/>
+      <c r="J22" s="67" t="n"/>
+      <c r="K22" s="67" t="n"/>
+      <c r="L22" s="68" t="n"/>
+      <c r="M22" s="68" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="74" t="inlineStr">
+        <is>
+          <t>Cultural services (SEEA EA 6.6)</t>
+        </is>
+      </c>
+      <c r="B23" s="75" t="n"/>
+      <c r="C23" s="75" t="n"/>
+      <c r="D23" s="75" t="n"/>
+      <c r="E23" s="75" t="n"/>
+      <c r="F23" s="75" t="n"/>
+      <c r="G23" s="75" t="n"/>
+      <c r="H23" s="75" t="n"/>
+      <c r="I23" s="75" t="n"/>
+      <c r="J23" s="75" t="n"/>
+      <c r="K23" s="75" t="n"/>
+      <c r="L23" s="75" t="n"/>
+      <c r="M23" s="75" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="65" t="inlineStr">
+        <is>
+          <t>Recreation &amp; tourism</t>
+        </is>
+      </c>
+      <c r="B24" s="66" t="inlineStr">
         <is>
           <t>visitors/yr</t>
         </is>
       </c>
-      <c r="C14" s="35" t="n"/>
-      <c r="D14" s="35" t="n"/>
-      <c r="E14" s="35" t="n"/>
-      <c r="F14" s="35" t="n"/>
-      <c r="G14" s="35" t="n"/>
-      <c r="H14" s="35" t="n"/>
-      <c r="I14" s="35" t="n"/>
-      <c r="J14" s="35" t="n"/>
-      <c r="K14" s="35" t="n"/>
-      <c r="L14" s="35" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="32" t="inlineStr">
-        <is>
-          <t>Gleaning</t>
-        </is>
-      </c>
-      <c r="B15" s="58" t="inlineStr">
+      <c r="C24" s="68" t="n"/>
+      <c r="D24" s="68" t="n"/>
+      <c r="E24" s="68" t="n"/>
+      <c r="F24" s="68" t="n"/>
+      <c r="G24" s="68" t="n"/>
+      <c r="H24" s="68" t="n"/>
+      <c r="I24" s="67" t="n"/>
+      <c r="J24" s="67" t="n"/>
+      <c r="K24" s="67" t="n"/>
+      <c r="L24" s="68" t="n"/>
+      <c r="M24" s="68" t="n"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="65" t="inlineStr">
+        <is>
+          <t>Gleaning (subsistence harvest)</t>
+        </is>
+      </c>
+      <c r="B25" s="66" t="inlineStr">
         <is>
           <t>hours/yr</t>
         </is>
       </c>
-      <c r="C15" s="35" t="n"/>
-      <c r="D15" s="35" t="n"/>
-      <c r="E15" s="35" t="n"/>
-      <c r="F15" s="35" t="n"/>
-      <c r="G15" s="35" t="n"/>
-      <c r="H15" s="35" t="n"/>
-      <c r="I15" s="35" t="n"/>
-      <c r="J15" s="35" t="n"/>
-      <c r="K15" s="35" t="n"/>
-      <c r="L15" s="35" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="51" t="inlineStr">
-        <is>
-          <t>Monetary Combined Supply and Use Table (USD/yr)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="52" t="n"/>
-      <c r="B19" s="52" t="n"/>
-      <c r="C19" s="31" t="inlineStr">
-        <is>
-          <t>SUPPLY (by ecosystem)</t>
-        </is>
-      </c>
-      <c r="D19" s="53" t="n"/>
-      <c r="E19" s="53" t="n"/>
-      <c r="F19" s="53" t="n"/>
-      <c r="G19" s="54" t="inlineStr">
-        <is>
-          <t>USE (by beneficiary)</t>
-        </is>
-      </c>
-      <c r="H19" s="52" t="n"/>
-      <c r="I19" s="52" t="n"/>
-      <c r="J19" s="52" t="n"/>
-      <c r="K19" s="52" t="n"/>
-      <c r="L19" s="52" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="55" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="B20" s="31" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="C20" s="56" t="inlineStr">
-        <is>
-          <t>Coral reefs</t>
-        </is>
-      </c>
-      <c r="D20" s="56" t="inlineStr">
-        <is>
-          <t>Seagrass</t>
-        </is>
-      </c>
-      <c r="E20" s="56" t="inlineStr">
-        <is>
-          <t>Mangroves</t>
-        </is>
-      </c>
-      <c r="F20" s="56" t="inlineStr">
-        <is>
-          <t>Total supply</t>
-        </is>
-      </c>
-      <c r="G20" s="57" t="inlineStr">
-        <is>
-          <t>Fisheries</t>
-        </is>
-      </c>
-      <c r="H20" s="57" t="inlineStr">
-        <is>
-          <t>Tourism</t>
-        </is>
-      </c>
-      <c r="I20" s="57" t="inlineStr">
-        <is>
-          <t>Coastal HH</t>
-        </is>
-      </c>
-      <c r="J20" s="57" t="inlineStr">
-        <is>
-          <t>Govt</t>
-        </is>
-      </c>
-      <c r="K20" s="57" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="L20" s="57" t="inlineStr">
-        <is>
-          <t>Total use</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="32" t="inlineStr">
-        <is>
-          <t>Fish provisioning</t>
-        </is>
-      </c>
-      <c r="B21" s="58" t="inlineStr">
-        <is>
-          <t>USD/yr</t>
-        </is>
-      </c>
-      <c r="C21" s="35" t="n"/>
-      <c r="D21" s="35" t="n"/>
-      <c r="E21" s="35" t="n"/>
-      <c r="F21" s="35" t="n"/>
-      <c r="G21" s="35" t="n"/>
-      <c r="H21" s="35" t="n"/>
-      <c r="I21" s="35" t="n"/>
-      <c r="J21" s="35" t="n"/>
-      <c r="K21" s="35" t="n"/>
-      <c r="L21" s="35" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="32" t="inlineStr">
-        <is>
-          <t>Carbon sequestration</t>
-        </is>
-      </c>
-      <c r="B22" s="58" t="inlineStr">
-        <is>
-          <t>USD/yr</t>
-        </is>
-      </c>
-      <c r="C22" s="35" t="n"/>
-      <c r="D22" s="35" t="n"/>
-      <c r="E22" s="35" t="n"/>
-      <c r="F22" s="35" t="n"/>
-      <c r="G22" s="35" t="n"/>
-      <c r="H22" s="35" t="n"/>
-      <c r="I22" s="35" t="n"/>
-      <c r="J22" s="35" t="n"/>
-      <c r="K22" s="35" t="n"/>
-      <c r="L22" s="35" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="32" t="inlineStr">
-        <is>
-          <t>Coastal protection</t>
-        </is>
-      </c>
-      <c r="B23" s="58" t="inlineStr">
-        <is>
-          <t>USD/yr</t>
-        </is>
-      </c>
-      <c r="C23" s="35" t="n"/>
-      <c r="D23" s="35" t="n"/>
-      <c r="E23" s="35" t="n"/>
-      <c r="F23" s="35" t="n"/>
-      <c r="G23" s="35" t="n"/>
-      <c r="H23" s="35" t="n"/>
-      <c r="I23" s="35" t="n"/>
-      <c r="J23" s="35" t="n"/>
-      <c r="K23" s="35" t="n"/>
-      <c r="L23" s="35" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="32" t="inlineStr">
-        <is>
-          <t>Nursery habitat</t>
-        </is>
-      </c>
-      <c r="B24" s="58" t="inlineStr">
-        <is>
-          <t>USD/yr</t>
-        </is>
-      </c>
-      <c r="C24" s="35" t="n"/>
-      <c r="D24" s="35" t="n"/>
-      <c r="E24" s="35" t="n"/>
-      <c r="F24" s="35" t="n"/>
-      <c r="G24" s="35" t="n"/>
-      <c r="H24" s="35" t="n"/>
-      <c r="I24" s="35" t="n"/>
-      <c r="J24" s="35" t="n"/>
-      <c r="K24" s="35" t="n"/>
-      <c r="L24" s="35" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="32" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
-      <c r="B25" s="58" t="inlineStr">
-        <is>
-          <t>USD/yr</t>
-        </is>
-      </c>
-      <c r="C25" s="35" t="n"/>
-      <c r="D25" s="35" t="n"/>
-      <c r="E25" s="35" t="n"/>
-      <c r="F25" s="35" t="n"/>
-      <c r="G25" s="35" t="n"/>
-      <c r="H25" s="35" t="n"/>
-      <c r="I25" s="35" t="n"/>
-      <c r="J25" s="35" t="n"/>
-      <c r="K25" s="35" t="n"/>
-      <c r="L25" s="35" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="32" t="inlineStr">
-        <is>
-          <t>Gleaning</t>
-        </is>
-      </c>
-      <c r="B26" s="58" t="inlineStr">
-        <is>
-          <t>USD/yr</t>
-        </is>
-      </c>
-      <c r="C26" s="35" t="n"/>
-      <c r="D26" s="35" t="n"/>
-      <c r="E26" s="35" t="n"/>
-      <c r="F26" s="35" t="n"/>
-      <c r="G26" s="35" t="n"/>
-      <c r="H26" s="35" t="n"/>
-      <c r="I26" s="35" t="n"/>
-      <c r="J26" s="35" t="n"/>
-      <c r="K26" s="35" t="n"/>
-      <c r="L26" s="35" t="n"/>
+      <c r="C25" s="68" t="n"/>
+      <c r="D25" s="68" t="n"/>
+      <c r="E25" s="68" t="n"/>
+      <c r="F25" s="68" t="n"/>
+      <c r="G25" s="68" t="n"/>
+      <c r="H25" s="68" t="n"/>
+      <c r="I25" s="67" t="n"/>
+      <c r="J25" s="67" t="n"/>
+      <c r="K25" s="67" t="n"/>
+      <c r="L25" s="68" t="n"/>
+      <c r="M25" s="68" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="76" t="inlineStr">
+        <is>
+          <t>Note: Format follows SEEA EA Table 7.1 (supply and use of ecosystem services). Carbon sequestration use allocated to Global/Exports as the benefit accrues globally.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A7:L7"/>
-    <mergeCell ref="G19:L19"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="G8:L8"/>
-    <mergeCell ref="A18:L18"/>
-    <mergeCell ref="C19:F19"/>
+  <mergeCells count="15">
+    <mergeCell ref="A28:M28"/>
+    <mergeCell ref="A19:M19"/>
+    <mergeCell ref="A14:M14"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A23:M23"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="A17:M17"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="A10:M10"/>
+    <mergeCell ref="C15:H15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/s-s-event-bogor/sessions/day-2/clinic/services/services_exercise.xlsx
+++ b/s-s-event-bogor/sessions/day-2/clinic/services/services_exercise.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Step 5 - Final Tables" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Step 6 - Use Tables" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answers" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Step 7 - Combined Table" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Step 7 - SUT" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,7 +28,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -152,8 +152,33 @@
       <color rgb="00404040"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="0030302F"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="0030302F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="0030302F"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -219,6 +244,36 @@
       <patternFill patternType="solid">
         <fgColor rgb="00B2D8D8"/>
         <bgColor rgb="00B2D8D8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00404040"/>
+        <bgColor rgb="00404040"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A8D5C2"/>
+        <bgColor rgb="00A8D5C2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007FBCBD"/>
+        <bgColor rgb="007FBCBD"/>
       </patternFill>
     </fill>
   </fills>
@@ -292,7 +347,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -479,6 +534,40 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5426,10 +5515,11 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="003B9C7B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -5438,653 +5528,592 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="59" t="inlineStr">
-        <is>
-          <t>SUPPLY TABLE (Table 7.1a)</t>
-        </is>
-      </c>
-      <c r="B1" s="60" t="n"/>
-      <c r="C1" s="60" t="n"/>
-      <c r="D1" s="60" t="n"/>
-      <c r="E1" s="60" t="n"/>
-      <c r="F1" s="60" t="n"/>
-      <c r="G1" s="60" t="n"/>
-      <c r="H1" s="60" t="n"/>
-      <c r="I1" s="60" t="n"/>
-      <c r="J1" s="60" t="n"/>
-      <c r="K1" s="60" t="n"/>
-      <c r="L1" s="60" t="n"/>
-      <c r="M1" s="60" t="n"/>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="53" t="n"/>
-      <c r="B2" s="53" t="n"/>
-      <c r="C2" s="61" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="77" t="inlineStr">
+        <is>
+          <t>Ecosystem Services Supply-Use Table (SEEA EA Table 7.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="78" t="inlineStr">
+        <is>
+          <t>Integrated supply and use account for ocean ecosystem services</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="79" t="inlineStr"/>
+      <c r="B4" s="79" t="inlineStr"/>
+      <c r="C4" s="79" t="inlineStr">
         <is>
           <t>Economic units</t>
         </is>
       </c>
-      <c r="D2" s="53" t="n"/>
-      <c r="E2" s="53" t="n"/>
-      <c r="F2" s="53" t="n"/>
-      <c r="G2" s="53" t="n"/>
-      <c r="H2" s="53" t="n"/>
-      <c r="I2" s="61" t="inlineStr">
+      <c r="D4" s="20" t="n"/>
+      <c r="E4" s="20" t="n"/>
+      <c r="F4" s="20" t="n"/>
+      <c r="G4" s="20" t="n"/>
+      <c r="H4" s="21" t="n"/>
+      <c r="I4" s="79" t="inlineStr">
         <is>
           <t>Ecosystem types</t>
         </is>
       </c>
-      <c r="J2" s="53" t="n"/>
-      <c r="K2" s="53" t="n"/>
-      <c r="L2" s="53" t="n"/>
-      <c r="M2" s="53" t="n"/>
-    </row>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" s="62" t="inlineStr">
+      <c r="J4" s="20" t="n"/>
+      <c r="K4" s="21" t="n"/>
+      <c r="L4" s="79" t="inlineStr"/>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="79" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="B3" s="62" t="inlineStr">
+      <c r="B5" s="79" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="C3" s="62" t="inlineStr">
-        <is>
-          <t>Fisheries</t>
-        </is>
-      </c>
-      <c r="D3" s="62" t="inlineStr">
-        <is>
-          <t>Tourism</t>
-        </is>
-      </c>
-      <c r="E3" s="62" t="inlineStr">
-        <is>
-          <t>Other industry</t>
-        </is>
-      </c>
-      <c r="F3" s="62" t="inlineStr">
+      <c r="C5" s="79" t="inlineStr">
+        <is>
+          <t>Fisheries
+sector</t>
+        </is>
+      </c>
+      <c r="D5" s="79" t="inlineStr">
+        <is>
+          <t>Tourism
+sector</t>
+        </is>
+      </c>
+      <c r="E5" s="79" t="inlineStr">
+        <is>
+          <t>Other
+industries</t>
+        </is>
+      </c>
+      <c r="F5" s="79" t="inlineStr">
         <is>
           <t>Households</t>
         </is>
       </c>
-      <c r="G3" s="62" t="inlineStr">
-        <is>
-          <t>Govt</t>
-        </is>
-      </c>
-      <c r="H3" s="62" t="inlineStr">
-        <is>
-          <t>Global/Exports</t>
-        </is>
-      </c>
-      <c r="I3" s="62" t="inlineStr">
+      <c r="G5" s="79" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="H5" s="79" t="inlineStr">
+        <is>
+          <t>Exports /
+Global</t>
+        </is>
+      </c>
+      <c r="I5" s="79" t="inlineStr">
         <is>
           <t>Coral reefs
 (M1.3)</t>
         </is>
       </c>
-      <c r="J3" s="62" t="inlineStr">
-        <is>
-          <t>Seagrass meadows
+      <c r="J5" s="79" t="inlineStr">
+        <is>
+          <t>Seagrass
+meadows
 (M1.1)</t>
         </is>
       </c>
-      <c r="K3" s="62" t="inlineStr">
+      <c r="K5" s="79" t="inlineStr">
         <is>
           <t>Mangroves
 (MFT1.2)</t>
         </is>
       </c>
-      <c r="L3" s="62" t="inlineStr">
-        <is>
-          <t>Total ecosystem</t>
-        </is>
-      </c>
-      <c r="M3" s="62" t="inlineStr">
+      <c r="L5" s="79" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="63" t="inlineStr">
-        <is>
-          <t>Provisioning services (SEEA EA 6.1)</t>
-        </is>
-      </c>
-      <c r="B4" s="64" t="n"/>
-      <c r="C4" s="64" t="n"/>
-      <c r="D4" s="64" t="n"/>
-      <c r="E4" s="64" t="n"/>
-      <c r="F4" s="64" t="n"/>
-      <c r="G4" s="64" t="n"/>
-      <c r="H4" s="64" t="n"/>
-      <c r="I4" s="64" t="n"/>
-      <c r="J4" s="64" t="n"/>
-      <c r="K4" s="64" t="n"/>
-      <c r="L4" s="64" t="n"/>
-      <c r="M4" s="64" t="n"/>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="65" t="inlineStr">
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="80" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="n"/>
+      <c r="C6" s="20" t="n"/>
+      <c r="D6" s="20" t="n"/>
+      <c r="E6" s="20" t="n"/>
+      <c r="F6" s="20" t="n"/>
+      <c r="G6" s="20" t="n"/>
+      <c r="H6" s="20" t="n"/>
+      <c r="I6" s="20" t="n"/>
+      <c r="J6" s="20" t="n"/>
+      <c r="K6" s="20" t="n"/>
+      <c r="L6" s="21" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="81" t="inlineStr">
+        <is>
+          <t>Provisioning (SEEA EA 6.1)</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="n"/>
+      <c r="C7" s="20" t="n"/>
+      <c r="D7" s="20" t="n"/>
+      <c r="E7" s="20" t="n"/>
+      <c r="F7" s="20" t="n"/>
+      <c r="G7" s="20" t="n"/>
+      <c r="H7" s="20" t="n"/>
+      <c r="I7" s="20" t="n"/>
+      <c r="J7" s="20" t="n"/>
+      <c r="K7" s="20" t="n"/>
+      <c r="L7" s="21" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="82" t="inlineStr">
         <is>
           <t>Fish provisioning</t>
         </is>
       </c>
-      <c r="B5" s="66" t="inlineStr">
-        <is>
-          <t>kg/yr</t>
-        </is>
-      </c>
-      <c r="C5" s="67" t="n"/>
-      <c r="D5" s="67" t="n"/>
-      <c r="E5" s="67" t="n"/>
-      <c r="F5" s="67" t="n"/>
-      <c r="G5" s="67" t="n"/>
-      <c r="H5" s="67" t="n"/>
-      <c r="I5" s="68" t="n"/>
-      <c r="J5" s="68" t="n"/>
-      <c r="K5" s="68" t="n"/>
-      <c r="L5" s="68" t="n"/>
-      <c r="M5" s="68" t="n"/>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="63" t="inlineStr">
-        <is>
-          <t>Regulating &amp; maintenance services (SEEA EA 6.2-6.5)</t>
-        </is>
-      </c>
-      <c r="B6" s="64" t="n"/>
-      <c r="C6" s="64" t="n"/>
-      <c r="D6" s="64" t="n"/>
-      <c r="E6" s="64" t="n"/>
-      <c r="F6" s="64" t="n"/>
-      <c r="G6" s="64" t="n"/>
-      <c r="H6" s="64" t="n"/>
-      <c r="I6" s="64" t="n"/>
-      <c r="J6" s="64" t="n"/>
-      <c r="K6" s="64" t="n"/>
-      <c r="L6" s="64" t="n"/>
-      <c r="M6" s="64" t="n"/>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="65" t="inlineStr">
+      <c r="B8" s="83" t="inlineStr">
+        <is>
+          <t>tonnes</t>
+        </is>
+      </c>
+      <c r="C8" s="84" t="n"/>
+      <c r="D8" s="84" t="n"/>
+      <c r="E8" s="84" t="n"/>
+      <c r="F8" s="84" t="n"/>
+      <c r="G8" s="84" t="n"/>
+      <c r="H8" s="84" t="n"/>
+      <c r="I8" s="35" t="n"/>
+      <c r="J8" s="35" t="n"/>
+      <c r="K8" s="35" t="n"/>
+      <c r="L8" s="85">
+        <f>SUM(I8:K8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="81" t="inlineStr">
+        <is>
+          <t>Regulating (SEEA EA 6.2-6.5)</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="n"/>
+      <c r="C9" s="20" t="n"/>
+      <c r="D9" s="20" t="n"/>
+      <c r="E9" s="20" t="n"/>
+      <c r="F9" s="20" t="n"/>
+      <c r="G9" s="20" t="n"/>
+      <c r="H9" s="20" t="n"/>
+      <c r="I9" s="20" t="n"/>
+      <c r="J9" s="20" t="n"/>
+      <c r="K9" s="20" t="n"/>
+      <c r="L9" s="21" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="82" t="inlineStr">
         <is>
           <t>Carbon sequestration</t>
         </is>
       </c>
-      <c r="B7" s="66" t="inlineStr">
-        <is>
-          <t>Mg CO₂/yr</t>
-        </is>
-      </c>
-      <c r="C7" s="67" t="n"/>
-      <c r="D7" s="67" t="n"/>
-      <c r="E7" s="67" t="n"/>
-      <c r="F7" s="67" t="n"/>
-      <c r="G7" s="67" t="n"/>
-      <c r="H7" s="67" t="n"/>
-      <c r="I7" s="68" t="n"/>
-      <c r="J7" s="68" t="n"/>
-      <c r="K7" s="68" t="n"/>
-      <c r="L7" s="68" t="n"/>
-      <c r="M7" s="68" t="n"/>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="65" t="inlineStr">
+      <c r="B10" s="83" t="inlineStr">
+        <is>
+          <t>tCO₂/yr</t>
+        </is>
+      </c>
+      <c r="C10" s="84" t="n"/>
+      <c r="D10" s="84" t="n"/>
+      <c r="E10" s="84" t="n"/>
+      <c r="F10" s="84" t="n"/>
+      <c r="G10" s="84" t="n"/>
+      <c r="H10" s="84" t="n"/>
+      <c r="I10" s="35" t="n"/>
+      <c r="J10" s="35" t="n"/>
+      <c r="K10" s="35" t="n"/>
+      <c r="L10" s="85">
+        <f>SUM(I10:K10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="82" t="inlineStr">
         <is>
           <t>Coastal protection</t>
         </is>
       </c>
-      <c r="B8" s="66" t="inlineStr">
-        <is>
-          <t>m of coastline</t>
-        </is>
-      </c>
-      <c r="C8" s="67" t="n"/>
-      <c r="D8" s="67" t="n"/>
-      <c r="E8" s="67" t="n"/>
-      <c r="F8" s="67" t="n"/>
-      <c r="G8" s="67" t="n"/>
-      <c r="H8" s="67" t="n"/>
-      <c r="I8" s="68" t="n"/>
-      <c r="J8" s="68" t="n"/>
-      <c r="K8" s="68" t="n"/>
-      <c r="L8" s="68" t="n"/>
-      <c r="M8" s="68" t="n"/>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="65" t="inlineStr">
-        <is>
-          <t>Nursery habitat support</t>
-        </is>
-      </c>
-      <c r="B9" s="66" t="inlineStr">
-        <is>
-          <t>kg fish/yr</t>
-        </is>
-      </c>
-      <c r="C9" s="67" t="n"/>
-      <c r="D9" s="67" t="n"/>
-      <c r="E9" s="67" t="n"/>
-      <c r="F9" s="67" t="n"/>
-      <c r="G9" s="67" t="n"/>
-      <c r="H9" s="67" t="n"/>
-      <c r="I9" s="68" t="n"/>
-      <c r="J9" s="68" t="n"/>
-      <c r="K9" s="68" t="n"/>
-      <c r="L9" s="68" t="n"/>
-      <c r="M9" s="68" t="n"/>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="63" t="inlineStr">
-        <is>
-          <t>Cultural services (SEEA EA 6.6)</t>
-        </is>
-      </c>
-      <c r="B10" s="64" t="n"/>
-      <c r="C10" s="64" t="n"/>
-      <c r="D10" s="64" t="n"/>
-      <c r="E10" s="64" t="n"/>
-      <c r="F10" s="64" t="n"/>
-      <c r="G10" s="64" t="n"/>
-      <c r="H10" s="64" t="n"/>
-      <c r="I10" s="64" t="n"/>
-      <c r="J10" s="64" t="n"/>
-      <c r="K10" s="64" t="n"/>
-      <c r="L10" s="64" t="n"/>
-      <c r="M10" s="64" t="n"/>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="65" t="inlineStr">
-        <is>
-          <t>Recreation &amp; tourism</t>
-        </is>
-      </c>
-      <c r="B11" s="66" t="inlineStr">
-        <is>
-          <t>visitors/yr</t>
-        </is>
-      </c>
-      <c r="C11" s="67" t="n"/>
-      <c r="D11" s="67" t="n"/>
-      <c r="E11" s="67" t="n"/>
-      <c r="F11" s="67" t="n"/>
-      <c r="G11" s="67" t="n"/>
-      <c r="H11" s="67" t="n"/>
-      <c r="I11" s="68" t="n"/>
-      <c r="J11" s="68" t="n"/>
-      <c r="K11" s="68" t="n"/>
-      <c r="L11" s="68" t="n"/>
-      <c r="M11" s="68" t="n"/>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="65" t="inlineStr">
-        <is>
-          <t>Gleaning (subsistence harvest)</t>
-        </is>
-      </c>
-      <c r="B12" s="66" t="inlineStr">
-        <is>
-          <t>hours/yr</t>
-        </is>
-      </c>
-      <c r="C12" s="67" t="n"/>
-      <c r="D12" s="67" t="n"/>
-      <c r="E12" s="67" t="n"/>
-      <c r="F12" s="67" t="n"/>
-      <c r="G12" s="67" t="n"/>
-      <c r="H12" s="67" t="n"/>
-      <c r="I12" s="68" t="n"/>
-      <c r="J12" s="68" t="n"/>
-      <c r="K12" s="68" t="n"/>
-      <c r="L12" s="68" t="n"/>
-      <c r="M12" s="68" t="n"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="69" t="inlineStr">
-        <is>
-          <t>USE TABLE (Table 7.1b)</t>
-        </is>
-      </c>
-      <c r="B14" s="70" t="n"/>
-      <c r="C14" s="70" t="n"/>
-      <c r="D14" s="70" t="n"/>
-      <c r="E14" s="70" t="n"/>
-      <c r="F14" s="70" t="n"/>
-      <c r="G14" s="70" t="n"/>
-      <c r="H14" s="70" t="n"/>
-      <c r="I14" s="70" t="n"/>
-      <c r="J14" s="70" t="n"/>
-      <c r="K14" s="70" t="n"/>
-      <c r="L14" s="70" t="n"/>
-      <c r="M14" s="70" t="n"/>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="71" t="n"/>
-      <c r="B15" s="71" t="n"/>
-      <c r="C15" s="72" t="inlineStr">
-        <is>
-          <t>Economic units</t>
-        </is>
-      </c>
-      <c r="D15" s="71" t="n"/>
-      <c r="E15" s="71" t="n"/>
-      <c r="F15" s="71" t="n"/>
-      <c r="G15" s="71" t="n"/>
-      <c r="H15" s="71" t="n"/>
-      <c r="I15" s="72" t="inlineStr">
-        <is>
-          <t>Ecosystem types</t>
-        </is>
-      </c>
-      <c r="J15" s="71" t="n"/>
-      <c r="K15" s="71" t="n"/>
-      <c r="L15" s="71" t="n"/>
-      <c r="M15" s="71" t="n"/>
-    </row>
-    <row r="16" ht="40" customHeight="1">
-      <c r="A16" s="73" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="B16" s="73" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="C16" s="73" t="inlineStr">
-        <is>
-          <t>Fisheries</t>
-        </is>
-      </c>
-      <c r="D16" s="73" t="inlineStr">
-        <is>
-          <t>Tourism</t>
-        </is>
-      </c>
-      <c r="E16" s="73" t="inlineStr">
-        <is>
-          <t>Other industry</t>
-        </is>
-      </c>
-      <c r="F16" s="73" t="inlineStr">
-        <is>
-          <t>Households</t>
-        </is>
-      </c>
-      <c r="G16" s="73" t="inlineStr">
-        <is>
-          <t>Govt</t>
-        </is>
-      </c>
-      <c r="H16" s="73" t="inlineStr">
-        <is>
-          <t>Global/Exports</t>
-        </is>
-      </c>
-      <c r="I16" s="73" t="inlineStr">
-        <is>
-          <t>Coral reefs
-(M1.3)</t>
-        </is>
-      </c>
-      <c r="J16" s="73" t="inlineStr">
-        <is>
-          <t>Seagrass meadows
-(M1.1)</t>
-        </is>
-      </c>
-      <c r="K16" s="73" t="inlineStr">
-        <is>
-          <t>Mangroves
-(MFT1.2)</t>
-        </is>
-      </c>
-      <c r="L16" s="73" t="inlineStr">
-        <is>
-          <t>Total ecosystem</t>
-        </is>
-      </c>
-      <c r="M16" s="73" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="74" t="inlineStr">
-        <is>
-          <t>Provisioning services (SEEA EA 6.1)</t>
-        </is>
-      </c>
-      <c r="B17" s="75" t="n"/>
-      <c r="C17" s="75" t="n"/>
-      <c r="D17" s="75" t="n"/>
-      <c r="E17" s="75" t="n"/>
-      <c r="F17" s="75" t="n"/>
-      <c r="G17" s="75" t="n"/>
-      <c r="H17" s="75" t="n"/>
-      <c r="I17" s="75" t="n"/>
-      <c r="J17" s="75" t="n"/>
-      <c r="K17" s="75" t="n"/>
-      <c r="L17" s="75" t="n"/>
-      <c r="M17" s="75" t="n"/>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="65" t="inlineStr">
+      <c r="B11" s="83" t="inlineStr">
+        <is>
+          <t>USD thousands</t>
+        </is>
+      </c>
+      <c r="C11" s="84" t="n"/>
+      <c r="D11" s="84" t="n"/>
+      <c r="E11" s="84" t="n"/>
+      <c r="F11" s="84" t="n"/>
+      <c r="G11" s="84" t="n"/>
+      <c r="H11" s="84" t="n"/>
+      <c r="I11" s="35" t="n"/>
+      <c r="J11" s="35" t="n"/>
+      <c r="K11" s="35" t="n"/>
+      <c r="L11" s="85">
+        <f>SUM(I11:K11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="82" t="inlineStr">
+        <is>
+          <t>Nursery habitat</t>
+        </is>
+      </c>
+      <c r="B12" s="83" t="inlineStr">
+        <is>
+          <t>hectares</t>
+        </is>
+      </c>
+      <c r="C12" s="84" t="n"/>
+      <c r="D12" s="84" t="n"/>
+      <c r="E12" s="84" t="n"/>
+      <c r="F12" s="84" t="n"/>
+      <c r="G12" s="84" t="n"/>
+      <c r="H12" s="84" t="n"/>
+      <c r="I12" s="35" t="n"/>
+      <c r="J12" s="35" t="n"/>
+      <c r="K12" s="35" t="n"/>
+      <c r="L12" s="85">
+        <f>SUM(I12:K12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="81" t="inlineStr">
+        <is>
+          <t>Cultural (SEEA EA 6.6)</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="n"/>
+      <c r="C13" s="20" t="n"/>
+      <c r="D13" s="20" t="n"/>
+      <c r="E13" s="20" t="n"/>
+      <c r="F13" s="20" t="n"/>
+      <c r="G13" s="20" t="n"/>
+      <c r="H13" s="20" t="n"/>
+      <c r="I13" s="20" t="n"/>
+      <c r="J13" s="20" t="n"/>
+      <c r="K13" s="20" t="n"/>
+      <c r="L13" s="21" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="82" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="B14" s="83" t="inlineStr">
+        <is>
+          <t>visitor-days</t>
+        </is>
+      </c>
+      <c r="C14" s="84" t="n"/>
+      <c r="D14" s="84" t="n"/>
+      <c r="E14" s="84" t="n"/>
+      <c r="F14" s="84" t="n"/>
+      <c r="G14" s="84" t="n"/>
+      <c r="H14" s="84" t="n"/>
+      <c r="I14" s="35" t="n"/>
+      <c r="J14" s="35" t="n"/>
+      <c r="K14" s="35" t="n"/>
+      <c r="L14" s="85">
+        <f>SUM(I14:K14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="82" t="inlineStr">
+        <is>
+          <t>Gleaning</t>
+        </is>
+      </c>
+      <c r="B15" s="83" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="C15" s="84" t="n"/>
+      <c r="D15" s="84" t="n"/>
+      <c r="E15" s="84" t="n"/>
+      <c r="F15" s="84" t="n"/>
+      <c r="G15" s="84" t="n"/>
+      <c r="H15" s="84" t="n"/>
+      <c r="I15" s="35" t="n"/>
+      <c r="J15" s="35" t="n"/>
+      <c r="K15" s="35" t="n"/>
+      <c r="L15" s="85">
+        <f>SUM(I15:K15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="86" t="n"/>
+      <c r="B16" s="86" t="n"/>
+      <c r="C16" s="86" t="n"/>
+      <c r="D16" s="86" t="n"/>
+      <c r="E16" s="86" t="n"/>
+      <c r="F16" s="86" t="n"/>
+      <c r="G16" s="86" t="n"/>
+      <c r="H16" s="86" t="n"/>
+      <c r="I16" s="86" t="n"/>
+      <c r="J16" s="86" t="n"/>
+      <c r="K16" s="86" t="n"/>
+      <c r="L16" s="86" t="n"/>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="87" t="inlineStr">
+        <is>
+          <t>USE</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="n"/>
+      <c r="C17" s="20" t="n"/>
+      <c r="D17" s="20" t="n"/>
+      <c r="E17" s="20" t="n"/>
+      <c r="F17" s="20" t="n"/>
+      <c r="G17" s="20" t="n"/>
+      <c r="H17" s="20" t="n"/>
+      <c r="I17" s="20" t="n"/>
+      <c r="J17" s="20" t="n"/>
+      <c r="K17" s="20" t="n"/>
+      <c r="L17" s="21" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="88" t="inlineStr">
+        <is>
+          <t>Provisioning (SEEA EA 6.1)</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="n"/>
+      <c r="C18" s="20" t="n"/>
+      <c r="D18" s="20" t="n"/>
+      <c r="E18" s="20" t="n"/>
+      <c r="F18" s="20" t="n"/>
+      <c r="G18" s="20" t="n"/>
+      <c r="H18" s="20" t="n"/>
+      <c r="I18" s="20" t="n"/>
+      <c r="J18" s="20" t="n"/>
+      <c r="K18" s="20" t="n"/>
+      <c r="L18" s="21" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="82" t="inlineStr">
         <is>
           <t>Fish provisioning</t>
         </is>
       </c>
-      <c r="B18" s="66" t="inlineStr">
-        <is>
-          <t>kg/yr</t>
-        </is>
-      </c>
-      <c r="C18" s="68" t="n"/>
-      <c r="D18" s="68" t="n"/>
-      <c r="E18" s="68" t="n"/>
-      <c r="F18" s="68" t="n"/>
-      <c r="G18" s="68" t="n"/>
-      <c r="H18" s="68" t="n"/>
-      <c r="I18" s="67" t="n"/>
-      <c r="J18" s="67" t="n"/>
-      <c r="K18" s="67" t="n"/>
-      <c r="L18" s="68" t="n"/>
-      <c r="M18" s="68" t="n"/>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="74" t="inlineStr">
-        <is>
-          <t>Regulating &amp; maintenance services (SEEA EA 6.2-6.5)</t>
-        </is>
-      </c>
-      <c r="B19" s="75" t="n"/>
-      <c r="C19" s="75" t="n"/>
-      <c r="D19" s="75" t="n"/>
-      <c r="E19" s="75" t="n"/>
-      <c r="F19" s="75" t="n"/>
-      <c r="G19" s="75" t="n"/>
-      <c r="H19" s="75" t="n"/>
-      <c r="I19" s="75" t="n"/>
-      <c r="J19" s="75" t="n"/>
-      <c r="K19" s="75" t="n"/>
-      <c r="L19" s="75" t="n"/>
-      <c r="M19" s="75" t="n"/>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="65" t="inlineStr">
+      <c r="B19" s="83" t="inlineStr">
+        <is>
+          <t>tonnes</t>
+        </is>
+      </c>
+      <c r="C19" s="35" t="n"/>
+      <c r="D19" s="35" t="n"/>
+      <c r="E19" s="35" t="n"/>
+      <c r="F19" s="35" t="n"/>
+      <c r="G19" s="35" t="n"/>
+      <c r="H19" s="35" t="n"/>
+      <c r="I19" s="84" t="n"/>
+      <c r="J19" s="84" t="n"/>
+      <c r="K19" s="84" t="n"/>
+      <c r="L19" s="85">
+        <f>SUM(C19:H19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="88" t="inlineStr">
+        <is>
+          <t>Regulating (SEEA EA 6.2-6.5)</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="n"/>
+      <c r="C20" s="20" t="n"/>
+      <c r="D20" s="20" t="n"/>
+      <c r="E20" s="20" t="n"/>
+      <c r="F20" s="20" t="n"/>
+      <c r="G20" s="20" t="n"/>
+      <c r="H20" s="20" t="n"/>
+      <c r="I20" s="20" t="n"/>
+      <c r="J20" s="20" t="n"/>
+      <c r="K20" s="20" t="n"/>
+      <c r="L20" s="21" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="82" t="inlineStr">
         <is>
           <t>Carbon sequestration</t>
         </is>
       </c>
-      <c r="B20" s="66" t="inlineStr">
-        <is>
-          <t>Mg CO₂/yr</t>
-        </is>
-      </c>
-      <c r="C20" s="68" t="n"/>
-      <c r="D20" s="68" t="n"/>
-      <c r="E20" s="68" t="n"/>
-      <c r="F20" s="68" t="n"/>
-      <c r="G20" s="68" t="n"/>
-      <c r="H20" s="68" t="n"/>
-      <c r="I20" s="67" t="n"/>
-      <c r="J20" s="67" t="n"/>
-      <c r="K20" s="67" t="n"/>
-      <c r="L20" s="68" t="n"/>
-      <c r="M20" s="68" t="n"/>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="65" t="inlineStr">
+      <c r="B21" s="83" t="inlineStr">
+        <is>
+          <t>tCO₂/yr</t>
+        </is>
+      </c>
+      <c r="C21" s="35" t="n"/>
+      <c r="D21" s="35" t="n"/>
+      <c r="E21" s="35" t="n"/>
+      <c r="F21" s="35" t="n"/>
+      <c r="G21" s="35" t="n"/>
+      <c r="H21" s="35" t="n"/>
+      <c r="I21" s="84" t="n"/>
+      <c r="J21" s="84" t="n"/>
+      <c r="K21" s="84" t="n"/>
+      <c r="L21" s="85">
+        <f>SUM(C21:H21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="82" t="inlineStr">
         <is>
           <t>Coastal protection</t>
         </is>
       </c>
-      <c r="B21" s="66" t="inlineStr">
-        <is>
-          <t>m of coastline</t>
-        </is>
-      </c>
-      <c r="C21" s="68" t="n"/>
-      <c r="D21" s="68" t="n"/>
-      <c r="E21" s="68" t="n"/>
-      <c r="F21" s="68" t="n"/>
-      <c r="G21" s="68" t="n"/>
-      <c r="H21" s="68" t="n"/>
-      <c r="I21" s="67" t="n"/>
-      <c r="J21" s="67" t="n"/>
-      <c r="K21" s="67" t="n"/>
-      <c r="L21" s="68" t="n"/>
-      <c r="M21" s="68" t="n"/>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="65" t="inlineStr">
-        <is>
-          <t>Nursery habitat support</t>
-        </is>
-      </c>
-      <c r="B22" s="66" t="inlineStr">
-        <is>
-          <t>kg fish/yr</t>
-        </is>
-      </c>
-      <c r="C22" s="68" t="n"/>
-      <c r="D22" s="68" t="n"/>
-      <c r="E22" s="68" t="n"/>
-      <c r="F22" s="68" t="n"/>
-      <c r="G22" s="68" t="n"/>
-      <c r="H22" s="68" t="n"/>
-      <c r="I22" s="67" t="n"/>
-      <c r="J22" s="67" t="n"/>
-      <c r="K22" s="67" t="n"/>
-      <c r="L22" s="68" t="n"/>
-      <c r="M22" s="68" t="n"/>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="74" t="inlineStr">
-        <is>
-          <t>Cultural services (SEEA EA 6.6)</t>
-        </is>
-      </c>
-      <c r="B23" s="75" t="n"/>
-      <c r="C23" s="75" t="n"/>
-      <c r="D23" s="75" t="n"/>
-      <c r="E23" s="75" t="n"/>
-      <c r="F23" s="75" t="n"/>
-      <c r="G23" s="75" t="n"/>
-      <c r="H23" s="75" t="n"/>
-      <c r="I23" s="75" t="n"/>
-      <c r="J23" s="75" t="n"/>
-      <c r="K23" s="75" t="n"/>
-      <c r="L23" s="75" t="n"/>
-      <c r="M23" s="75" t="n"/>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="65" t="inlineStr">
-        <is>
-          <t>Recreation &amp; tourism</t>
-        </is>
-      </c>
-      <c r="B24" s="66" t="inlineStr">
-        <is>
-          <t>visitors/yr</t>
-        </is>
-      </c>
-      <c r="C24" s="68" t="n"/>
-      <c r="D24" s="68" t="n"/>
-      <c r="E24" s="68" t="n"/>
-      <c r="F24" s="68" t="n"/>
-      <c r="G24" s="68" t="n"/>
-      <c r="H24" s="68" t="n"/>
-      <c r="I24" s="67" t="n"/>
-      <c r="J24" s="67" t="n"/>
-      <c r="K24" s="67" t="n"/>
-      <c r="L24" s="68" t="n"/>
-      <c r="M24" s="68" t="n"/>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="65" t="inlineStr">
-        <is>
-          <t>Gleaning (subsistence harvest)</t>
-        </is>
-      </c>
-      <c r="B25" s="66" t="inlineStr">
-        <is>
-          <t>hours/yr</t>
-        </is>
-      </c>
-      <c r="C25" s="68" t="n"/>
-      <c r="D25" s="68" t="n"/>
-      <c r="E25" s="68" t="n"/>
-      <c r="F25" s="68" t="n"/>
-      <c r="G25" s="68" t="n"/>
-      <c r="H25" s="68" t="n"/>
-      <c r="I25" s="67" t="n"/>
-      <c r="J25" s="67" t="n"/>
-      <c r="K25" s="67" t="n"/>
-      <c r="L25" s="68" t="n"/>
-      <c r="M25" s="68" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="76" t="inlineStr">
-        <is>
-          <t>Note: Format follows SEEA EA Table 7.1 (supply and use of ecosystem services). Carbon sequestration use allocated to Global/Exports as the benefit accrues globally.</t>
-        </is>
+      <c r="B22" s="83" t="inlineStr">
+        <is>
+          <t>USD thousands</t>
+        </is>
+      </c>
+      <c r="C22" s="35" t="n"/>
+      <c r="D22" s="35" t="n"/>
+      <c r="E22" s="35" t="n"/>
+      <c r="F22" s="35" t="n"/>
+      <c r="G22" s="35" t="n"/>
+      <c r="H22" s="35" t="n"/>
+      <c r="I22" s="84" t="n"/>
+      <c r="J22" s="84" t="n"/>
+      <c r="K22" s="84" t="n"/>
+      <c r="L22" s="85">
+        <f>SUM(C22:H22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="82" t="inlineStr">
+        <is>
+          <t>Nursery habitat</t>
+        </is>
+      </c>
+      <c r="B23" s="83" t="inlineStr">
+        <is>
+          <t>hectares</t>
+        </is>
+      </c>
+      <c r="C23" s="35" t="n"/>
+      <c r="D23" s="35" t="n"/>
+      <c r="E23" s="35" t="n"/>
+      <c r="F23" s="35" t="n"/>
+      <c r="G23" s="35" t="n"/>
+      <c r="H23" s="35" t="n"/>
+      <c r="I23" s="84" t="n"/>
+      <c r="J23" s="84" t="n"/>
+      <c r="K23" s="84" t="n"/>
+      <c r="L23" s="85">
+        <f>SUM(C23:H23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="88" t="inlineStr">
+        <is>
+          <t>Cultural (SEEA EA 6.6)</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="n"/>
+      <c r="C24" s="20" t="n"/>
+      <c r="D24" s="20" t="n"/>
+      <c r="E24" s="20" t="n"/>
+      <c r="F24" s="20" t="n"/>
+      <c r="G24" s="20" t="n"/>
+      <c r="H24" s="20" t="n"/>
+      <c r="I24" s="20" t="n"/>
+      <c r="J24" s="20" t="n"/>
+      <c r="K24" s="20" t="n"/>
+      <c r="L24" s="21" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="82" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="B25" s="83" t="inlineStr">
+        <is>
+          <t>visitor-days</t>
+        </is>
+      </c>
+      <c r="C25" s="35" t="n"/>
+      <c r="D25" s="35" t="n"/>
+      <c r="E25" s="35" t="n"/>
+      <c r="F25" s="35" t="n"/>
+      <c r="G25" s="35" t="n"/>
+      <c r="H25" s="35" t="n"/>
+      <c r="I25" s="84" t="n"/>
+      <c r="J25" s="84" t="n"/>
+      <c r="K25" s="84" t="n"/>
+      <c r="L25" s="85">
+        <f>SUM(C25:H25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="82" t="inlineStr">
+        <is>
+          <t>Gleaning</t>
+        </is>
+      </c>
+      <c r="B26" s="83" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="C26" s="35" t="n"/>
+      <c r="D26" s="35" t="n"/>
+      <c r="E26" s="35" t="n"/>
+      <c r="F26" s="35" t="n"/>
+      <c r="G26" s="35" t="n"/>
+      <c r="H26" s="35" t="n"/>
+      <c r="I26" s="84" t="n"/>
+      <c r="J26" s="84" t="n"/>
+      <c r="K26" s="84" t="n"/>
+      <c r="L26" s="85">
+        <f>SUM(C26:H26)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A28:M28"/>
-    <mergeCell ref="A19:M19"/>
-    <mergeCell ref="A14:M14"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A23:M23"/>
-    <mergeCell ref="A6:M6"/>
-    <mergeCell ref="A17:M17"/>
-    <mergeCell ref="A4:M4"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="A10:M10"/>
-    <mergeCell ref="C15:H15"/>
+  <mergeCells count="12">
+    <mergeCell ref="A20:L20"/>
+    <mergeCell ref="A24:L24"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A7:L7"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A13:L13"/>
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="A9:L9"/>
+    <mergeCell ref="A17:L17"/>
+    <mergeCell ref="A18:L18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/s-s-event-bogor/sessions/day-2/clinic/services/services_exercise.xlsx
+++ b/s-s-event-bogor/sessions/day-2/clinic/services/services_exercise.xlsx
@@ -935,7 +935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -1068,6 +1068,48 @@
       <c r="A26" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  - The use table total must match the supply table total</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Step 7: Build the integrated Supply-Use Table (SEEA EA Table 7.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Combines supply and use in one table</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - SUPPLY half: fill ecosystem columns (where services come from)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - USE half: fill economic unit columns (who benefits)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Check: Total supply = Total use for each service row</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - This is the standard SEEA EA output format</t>
         </is>
       </c>
     </row>
@@ -3392,6 +3434,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -3399,6 +3442,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
@@ -3406,6 +3450,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
@@ -3560,6 +3605,8 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
@@ -3567,6 +3614,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
@@ -3695,6 +3743,8 @@
         <v>17400</v>
       </c>
     </row>
+    <row r="23"/>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
@@ -3702,6 +3752,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
@@ -3787,6 +3838,8 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
@@ -3794,6 +3847,7 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
@@ -3846,6 +3900,7 @@
         <v>210000</v>
       </c>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
@@ -3909,6 +3964,7 @@
         <v>119085</v>
       </c>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
@@ -3961,6 +4017,7 @@
         <v>1550000</v>
       </c>
     </row>
+    <row r="50"/>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
@@ -4009,6 +4066,8 @@
         <v>1359000</v>
       </c>
     </row>
+    <row r="55"/>
+    <row r="56"/>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
@@ -4016,6 +4075,7 @@
         </is>
       </c>
     </row>
+    <row r="58"/>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
@@ -4164,6 +4224,7 @@
         <v>3238085</v>
       </c>
     </row>
+    <row r="65"/>
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
         <is>
@@ -4171,6 +4232,7 @@
         </is>
       </c>
     </row>
+    <row r="67"/>
     <row r="68">
       <c r="A68" s="19" t="inlineStr">
         <is>
@@ -4235,6 +4297,7 @@
       <c r="E71" s="20" t="n"/>
       <c r="F71" s="21" t="n"/>
     </row>
+    <row r="72"/>
     <row r="73">
       <c r="A73" s="40" t="inlineStr">
         <is>
@@ -4242,6 +4305,7 @@
         </is>
       </c>
     </row>
+    <row r="74"/>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
@@ -4291,6 +4355,7 @@
         </is>
       </c>
     </row>
+    <row r="82"/>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
@@ -4520,6 +4585,7 @@
         <v>18000</v>
       </c>
     </row>
+    <row r="91"/>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
@@ -4775,6 +4841,7 @@
         <v>3253835</v>
       </c>
     </row>
+    <row r="101"/>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
@@ -4789,6 +4856,7 @@
         </is>
       </c>
     </row>
+    <row r="104"/>
     <row r="105">
       <c r="A105" s="45" t="inlineStr">
         <is>
@@ -4796,6 +4864,8 @@
         </is>
       </c>
     </row>
+    <row r="106"/>
+    <row r="107"/>
     <row r="108">
       <c r="A108" s="40" t="inlineStr">
         <is>
@@ -4803,6 +4873,7 @@
         </is>
       </c>
     </row>
+    <row r="109"/>
     <row r="110">
       <c r="A110" s="47" t="inlineStr">
         <is>
@@ -5124,6 +5195,7 @@
         <v>18000</v>
       </c>
     </row>
+    <row r="118"/>
     <row r="119">
       <c r="A119" s="47" t="inlineStr">
         <is>
@@ -5487,6 +5559,7 @@
         <v>3253835</v>
       </c>
     </row>
+    <row r="128"/>
     <row r="129">
       <c r="A129" s="50" t="inlineStr">
         <is>
